--- a/output/pdf_financials_xlsx/LITH.xlsx
+++ b/output/pdf_financials_xlsx/LITH.xlsx
@@ -6151,37 +6151,37 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.634189</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.214477</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.25417</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.60494</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.045556</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-3.21546</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-1.336159</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.663834</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-1.548287</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-8.075322</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-22.142698</v>
       </c>
       <c r="M118" s="1" t="inlineStr">
         <is>
@@ -17278,7 +17278,11 @@
           <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -19569,7 +19573,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -20766,7 +20774,11 @@
           <t>Paid exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -24804,7 +24816,11 @@
           <t>Exploration and evaluation expenditures (308,810) -</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -26092,7 +26108,11 @@
           <t>Exploration and evaluation expenditures 131,806 -</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -27056,7 +27076,11 @@
           <t>Exploration and evaluation expenditures 482,576 -</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -27781,7 +27805,11 @@
           <t>Exploration and evaluation expenditures 522,269 -</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E260" s="5" t="n">
         <v>-0.634189</v>
       </c>

--- a/output/pdf_financials_xlsx/LITH.xlsx
+++ b/output/pdf_financials_xlsx/LITH.xlsx
@@ -863,28 +863,28 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.039857</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.081159</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1.031305</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>3.464636</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>2.364892</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>0.550807</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>4.642769</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>3.27421</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>6.992823</v>
@@ -915,28 +915,28 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.039857</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.081159</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0</v>
+        <v>-1.031305</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.09838</v>
+        <v>-3.366256</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.090506</v>
+        <v>-2.274386</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.00182</v>
+        <v>-0.548987</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.141009</v>
+        <v>-4.50176</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>2.221301</v>
+        <v>-1.052909</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-6.992823</v>
@@ -988,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>2.221301</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>1.185444</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1858,10 +1858,10 @@
         <v>-4.182477</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.624886</v>
+        <v>-4.846187</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.42013</v>
+        <v>-0.765314</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>11.367698</v>
@@ -1962,10 +1962,10 @@
         <v>-4.182477</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.61534</v>
+        <v>-4.836641</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.4557</v>
+        <v>-0.7297439999999999</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>11.367698</v>
@@ -2020,7 +2020,7 @@
         <v>-2966.106418739229</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-117.7391087475313</v>
+        <v>-217.7391087475313</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2166,13 +2166,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.002079</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.002862</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.126894</v>
@@ -2184,7 +2184,7 @@
         <v>2.566319</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.138445</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.568339</v>
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.103</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.002079</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.002862</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.126894</v>
@@ -2276,7 +2276,7 @@
         <v>2.566319</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.138445</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.568339</v>
@@ -2810,13 +2810,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.103</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.002079</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.002862</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>0.07852199999999999</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.39539</v>
+        <v>1.256945</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>1.212187</v>
@@ -13693,7 +13693,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -31547,7 +31547,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -31616,7 +31616,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -35936,7 +35936,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">

--- a/output/pdf_financials_xlsx/LITH.xlsx
+++ b/output/pdf_financials_xlsx/LITH.xlsx
@@ -1251,7 +1251,7 @@
         <v>-1.065496</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.047452</v>
+        <v>1.065496</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-2.01951</v>
@@ -2079,7 +2079,7 @@
         <v>-40.59208666585901</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>11.29459929069574</v>
+        <v>253.6110251588794</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>17.76533824174428</v>
@@ -5307,7 +5307,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002395</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.002196</v>
@@ -7077,7 +7077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q382"/>
+  <dimension ref="A1:Q383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14338,10 +14338,8 @@
       <c r="F92" s="5" t="n">
         <v>0.301489</v>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G92" s="5" t="n">
+        <v>0.09594800000000001</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -15760,10 +15758,8 @@
       <c r="F110" s="5" t="n">
         <v>1.223666</v>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G110" s="5" t="n">
+        <v>1.477836</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -15843,10 +15839,8 @@
       <c r="F111" s="5" t="n">
         <v>1.228144</v>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G111" s="5" t="n">
+        <v>1.482746</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -15926,10 +15920,8 @@
       <c r="F112" s="5" t="n">
         <v>0.06704499999999999</v>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G112" s="5" t="n">
+        <v>0.050201</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -16005,10 +15997,8 @@
       <c r="F113" s="5" t="n">
         <v>0.234444</v>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G113" s="5" t="n">
+        <v>0.045747</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -16074,7 +16064,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Share capital (note 5(b))</t>
+          <t>Share capital (note 5(b)</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -16082,16 +16072,16 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E114" s="5" t="n">
-        <v>1.169686</v>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F114" s="5" t="n">
         <v>1.544686</v>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G114" s="5" t="n">
+        <v>2.044686</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -16147,29 +16137,29 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OPERATING</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Net income (loss) $</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share capital (note 5(b))</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>1.169686</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>1.544686</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -16206,11 +16196,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N115" s="5" t="n">
-        <v>-2.118404</v>
-      </c>
-      <c r="O115" s="5" t="n">
-        <v>0.467582</v>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -16231,17 +16225,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Share-based compensation 10(e)</t>
+          <t>Net income (loss) $</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -16290,10 +16284,10 @@
         </is>
       </c>
       <c r="N116" s="5" t="n">
-        <v>2.371927</v>
+        <v>-2.118404</v>
       </c>
       <c r="O116" s="5" t="n">
-        <v>3.079847</v>
+        <v>0.467582</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -16319,10 +16313,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Net tax expense</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Share-based compensation 10(e)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -16369,10 +16367,10 @@
         </is>
       </c>
       <c r="N117" s="5" t="n">
-        <v>1.065496</v>
+        <v>2.371927</v>
       </c>
       <c r="O117" s="5" t="n">
-        <v>-0.047452</v>
+        <v>3.079847</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -16398,14 +16396,10 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Net tax expense</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -16452,10 +16446,10 @@
         </is>
       </c>
       <c r="N118" s="5" t="n">
-        <v>0.009546000000000001</v>
+        <v>1.065496</v>
       </c>
       <c r="O118" s="5" t="n">
-        <v>0.03557</v>
+        <v>-0.047452</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -16481,10 +16475,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Accretion of notes receivable 8</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -16531,12 +16529,10 @@
         </is>
       </c>
       <c r="N119" s="5" t="n">
-        <v>-0.199221</v>
-      </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009546000000000001</v>
+      </c>
+      <c r="O119" s="5" t="n">
+        <v>0.03557</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -16562,7 +16558,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities 7</t>
+          <t>Accretion of notes receivable 8</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -16612,10 +16608,12 @@
         </is>
       </c>
       <c r="N120" s="5" t="n">
-        <v>0.849405</v>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v>0.707788</v>
+        <v>-0.199221</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -16641,7 +16639,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Reversal of previously recognized discount on mining option 9</t>
+          <t>Unrealized loss on marketable securities 7</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -16690,13 +16688,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N121" s="5" t="n">
+        <v>0.849405</v>
       </c>
       <c r="O121" s="5" t="n">
-        <v>0.269382</v>
+        <v>0.707788</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -16722,7 +16718,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Loss on disposal of property 9</t>
+          <t>Reversal of previously recognized discount on mining option 9</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -16771,13 +16767,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N122" s="5" t="n">
-        <v>0.453577</v>
-      </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O122" s="5" t="n">
+        <v>0.269382</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -16803,7 +16799,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Interest income and other 8</t>
+          <t>Loss on disposal of property 9</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -16853,10 +16849,12 @@
         </is>
       </c>
       <c r="N123" s="5" t="n">
-        <v>-0.081646</v>
-      </c>
-      <c r="O123" s="5" t="n">
-        <v>-0.08</v>
+        <v>0.453577</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -16882,7 +16880,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange gain</t>
+          <t>Interest income and other 8</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -16932,10 +16930,10 @@
         </is>
       </c>
       <c r="N124" s="5" t="n">
-        <v>-0.748851</v>
+        <v>-0.081646</v>
       </c>
       <c r="O124" s="5" t="n">
-        <v>-2.298449</v>
+        <v>-0.08</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -16961,7 +16959,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Other income – gain on option agreement</t>
+          <t>Unrealized foreign exchange gain</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -17011,12 +17009,10 @@
         </is>
       </c>
       <c r="N125" s="5" t="n">
-        <v>-1.68821</v>
-      </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.748851</v>
+      </c>
+      <c r="O125" s="5" t="n">
+        <v>-2.298449</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -17042,7 +17038,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Change in net monetary position due to hyperinflation 2(b)</t>
+          <t>Other income – gain on option agreement</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -17092,10 +17088,12 @@
         </is>
       </c>
       <c r="N126" s="5" t="n">
-        <v>-0.418924</v>
-      </c>
-      <c r="O126" s="5" t="n">
-        <v>-4.214396</v>
+        <v>-1.68821</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -17121,14 +17119,10 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital 12</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Change in net monetary position due to hyperinflation 2(b)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -17175,10 +17169,10 @@
         </is>
       </c>
       <c r="N127" s="5" t="n">
-        <v>-0.26587</v>
+        <v>-0.418924</v>
       </c>
       <c r="O127" s="5" t="n">
-        <v>1.033958</v>
+        <v>-4.214396</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -17204,12 +17198,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cash flow used in operating activities</t>
+          <t>Change in non-cash working capital 12</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -17227,29 +17221,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H128" s="5" t="n">
-        <v>-0.030405</v>
-      </c>
-      <c r="I128" s="5" t="n">
-        <v>-0.5653550000000001</v>
-      </c>
-      <c r="J128" s="5" t="n">
-        <v>-3.147545</v>
-      </c>
-      <c r="K128" s="5" t="n">
-        <v>-0.946793</v>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v>-0.417198</v>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v>-2.132122</v>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N128" s="5" t="n">
-        <v>-0.7711750000000001</v>
+        <v>-0.26587</v>
       </c>
       <c r="O128" s="5" t="n">
-        <v>-1.04617</v>
+        <v>1.033958</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -17270,17 +17276,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>INVESTING</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 9</t>
+          <t>Cash flow used in operating activities</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -17298,41 +17304,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H129" s="5" t="n">
+        <v>-0.030405</v>
+      </c>
+      <c r="I129" s="5" t="n">
+        <v>-0.5653550000000001</v>
+      </c>
+      <c r="J129" s="5" t="n">
+        <v>-3.147545</v>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>-0.946793</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>-0.417198</v>
+      </c>
+      <c r="M129" s="5" t="n">
+        <v>-2.132122</v>
       </c>
       <c r="N129" s="5" t="n">
-        <v>-8.075322</v>
+        <v>-0.7711750000000001</v>
       </c>
       <c r="O129" s="5" t="n">
-        <v>-22.142698</v>
+        <v>-1.04617</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -17358,12 +17352,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Purchase of investment 6</t>
+          <t>Exploration and evaluation expenditures 9</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PurchaseOfInvestment</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -17412,10 +17406,10 @@
         </is>
       </c>
       <c r="N130" s="5" t="n">
-        <v>-19.7389</v>
+        <v>-8.075322</v>
       </c>
       <c r="O130" s="5" t="n">
-        <v>-0.35</v>
+        <v>-22.142698</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -17441,10 +17435,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Redemption of short term deposits</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Purchase of investment 6</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -17490,13 +17488,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N131" s="5" t="n">
+        <v>-19.7389</v>
       </c>
       <c r="O131" s="5" t="n">
-        <v>4.58797</v>
+        <v>-0.35</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -17522,7 +17518,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Due from related</t>
+          <t>Redemption of short term deposits</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -17576,10 +17572,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O132" s="5" t="n">
+        <v>4.58797</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
@@ -17605,7 +17599,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Property acquisition 9</t>
+          <t>Due from related</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -17654,11 +17648,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N133" s="5" t="n">
-        <v>-0.650039</v>
-      </c>
-      <c r="O133" s="5" t="n">
-        <v>-0.683874</v>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P133" t="inlineStr">
         <is>
@@ -17684,7 +17682,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Option payments received 9</t>
+          <t>Property acquisition 9</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -17734,12 +17732,10 @@
         </is>
       </c>
       <c r="N134" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.650039</v>
+      </c>
+      <c r="O134" s="5" t="n">
+        <v>-0.683874</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
@@ -17765,14 +17761,10 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Cash flow used in investing activities</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Option payments received 9</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -17798,23 +17790,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J135" s="5" t="n">
-        <v>-4.880538</v>
-      </c>
-      <c r="K135" s="5" t="n">
-        <v>-1.469074</v>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v>-0.5638339999999999</v>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v>-1.672904</v>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N135" s="5" t="n">
-        <v>-28.064261</v>
-      </c>
-      <c r="O135" s="5" t="n">
-        <v>-18.588602</v>
+        <v>0.4</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P135" t="inlineStr">
         <is>
@@ -17835,17 +17837,17 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>INVESTING</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Issuance of common shares 10</t>
+          <t>Cash flow used in investing activities</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -17873,33 +17875,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J136" s="5" t="n">
+        <v>-4.880538</v>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>-1.469074</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>-0.5638339999999999</v>
+      </c>
+      <c r="M136" s="5" t="n">
+        <v>-1.672904</v>
       </c>
       <c r="N136" s="5" t="n">
-        <v>34.952999</v>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-28.064261</v>
+      </c>
+      <c r="O136" s="5" t="n">
+        <v>-18.588602</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
@@ -17925,12 +17917,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Share issue costs 10</t>
+          <t>Issuance of common shares 10</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -17979,7 +17971,7 @@
         </is>
       </c>
       <c r="N137" s="5" t="n">
-        <v>-1.743499</v>
+        <v>34.952999</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -18010,10 +18002,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Exercised Unit and broker warrants 10</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>Share issue costs 10</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -18060,10 +18056,12 @@
         </is>
       </c>
       <c r="N138" s="5" t="n">
-        <v>5.220188</v>
-      </c>
-      <c r="O138" s="5" t="n">
-        <v>5.760691</v>
+        <v>-1.743499</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P138" t="inlineStr">
         <is>
@@ -18089,7 +18087,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Exercised stock options 10</t>
+          <t>Exercised Unit and broker warrants 10</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -18139,12 +18137,10 @@
         </is>
       </c>
       <c r="N139" s="5" t="n">
-        <v>0.40625</v>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.220188</v>
+      </c>
+      <c r="O139" s="5" t="n">
+        <v>5.760691</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
@@ -18170,14 +18166,10 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cash flow provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Exercised stock options 10</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -18213,17 +18205,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L140" s="5" t="n">
-        <v>1.410926</v>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v>10.170726</v>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N140" s="5" t="n">
-        <v>38.835938</v>
-      </c>
-      <c r="O140" s="5" t="n">
-        <v>5.760691</v>
+        <v>0.40625</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -18249,10 +18247,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Foreign exchange on cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Cash flow provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -18288,21 +18290,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L141" s="5" t="n">
+        <v>1.410926</v>
+      </c>
+      <c r="M141" s="5" t="n">
+        <v>10.170726</v>
       </c>
       <c r="N141" s="5" t="n">
-        <v>0.005456</v>
+        <v>38.835938</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>-0.472427</v>
+        <v>5.760691</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
@@ -18328,14 +18326,10 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Foreign exchange on cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -18382,10 +18376,10 @@
         </is>
       </c>
       <c r="N142" s="5" t="n">
-        <v>10.005958</v>
+        <v>0.005456</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>-14.346508</v>
+        <v>-0.472427</v>
       </c>
       <c r="P142" t="inlineStr">
         <is>
@@ -18411,12 +18405,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
+          <t>Change in cash and cash equivalents</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -18454,17 +18448,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L143" s="5" t="n">
-        <v>0.138445</v>
-      </c>
-      <c r="M143" s="5" t="n">
-        <v>0.568339</v>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N143" s="5" t="n">
-        <v>6.934039</v>
+        <v>10.005958</v>
       </c>
       <c r="O143" s="5" t="n">
-        <v>16.939997</v>
+        <v>-14.346508</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
@@ -18490,12 +18488,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -18523,23 +18521,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J144" s="5" t="n">
-        <v>2.566319</v>
-      </c>
-      <c r="K144" s="5" t="n">
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="n">
         <v>0.138445</v>
       </c>
-      <c r="L144" s="5" t="n">
+      <c r="M144" s="5" t="n">
         <v>0.568339</v>
       </c>
-      <c r="M144" s="5" t="n">
+      <c r="N144" s="5" t="n">
         <v>6.934039</v>
       </c>
-      <c r="N144" s="5" t="n">
+      <c r="O144" s="5" t="n">
         <v>16.939997</v>
-      </c>
-      <c r="O144" s="5" t="n">
-        <v>2.593489</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
@@ -18560,15 +18562,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents is comprised of</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Cash $</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -18584,26 +18590,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H145" s="5" t="n">
-        <v>0.126894</v>
-      </c>
-      <c r="I145" s="5" t="n">
-        <v>0.97827</v>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" s="5" t="n">
-        <v>0.549999</v>
+        <v>2.566319</v>
       </c>
       <c r="K145" s="5" t="n">
         <v>0.138445</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>0.538339</v>
+        <v>0.568339</v>
       </c>
       <c r="M145" s="5" t="n">
-        <v>2.903422</v>
+        <v>6.934039</v>
       </c>
       <c r="N145" s="5" t="n">
-        <v>4.499796</v>
+        <v>16.939997</v>
       </c>
       <c r="O145" s="5" t="n">
         <v>2.593489</v>
@@ -18632,7 +18642,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Term deposits and guaranteed investments</t>
+          <t>Cash $</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -18651,41 +18661,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H146" s="5" t="n">
+        <v>0.126894</v>
+      </c>
+      <c r="I146" s="5" t="n">
+        <v>0.97827</v>
+      </c>
+      <c r="J146" s="5" t="n">
+        <v>0.549999</v>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>0.138445</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>0.538339</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>4.030617</v>
+        <v>2.903422</v>
       </c>
       <c r="N146" s="5" t="n">
-        <v>12.440201</v>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.499796</v>
+      </c>
+      <c r="O146" s="5" t="n">
+        <v>2.593489</v>
       </c>
       <c r="P146" t="inlineStr">
         <is>
@@ -18711,7 +18709,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents is comprised of total</t>
+          <t>Term deposits and guaranteed investments</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -18730,29 +18728,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" s="5" t="n">
-        <v>0.126894</v>
-      </c>
-      <c r="I147" s="5" t="n">
-        <v>6.72827</v>
-      </c>
-      <c r="J147" s="5" t="n">
-        <v>2.566319</v>
-      </c>
-      <c r="K147" s="5" t="n">
-        <v>0.138445</v>
-      </c>
-      <c r="L147" s="5" t="n">
-        <v>0.538339</v>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="5" t="n">
-        <v>6.934039</v>
+        <v>4.030617</v>
       </c>
       <c r="N147" s="5" t="n">
-        <v>16.939997</v>
-      </c>
-      <c r="O147" s="5" t="n">
-        <v>2.593489</v>
+        <v>12.440201</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P147" t="inlineStr">
         <is>
@@ -18773,19 +18783,15 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OPERATING</t>
+          <t>Cash and cash equivalents is comprised of</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Cash and cash equivalents is comprised of total</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -18801,35 +18807,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H148" s="5" t="n">
+        <v>0.126894</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>6.72827</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>-3.366255</v>
+        <v>2.566319</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>-3.080952</v>
+        <v>0.138445</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>-0.648248</v>
+        <v>0.538339</v>
       </c>
       <c r="M148" s="5" t="n">
-        <v>-4.50176</v>
+        <v>6.934039</v>
       </c>
       <c r="N148" s="5" t="n">
-        <v>-2.118404</v>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>16.939997</v>
+      </c>
+      <c r="O148" s="5" t="n">
+        <v>2.593489</v>
       </c>
       <c r="P148" t="inlineStr">
         <is>
@@ -18850,17 +18850,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Share-based compensation 7(e)</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -18888,26 +18888,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J149" s="5" t="n">
+        <v>-3.366255</v>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>-3.080952</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>-0.648248</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>0.982468</v>
+        <v>-4.50176</v>
       </c>
       <c r="N149" s="5" t="n">
-        <v>2.371927</v>
+        <v>-2.118404</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -18938,10 +18932,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Current income tax expense</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
+          <t>Share-based compensation 7(e)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -18982,13 +18980,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M150" s="5" t="n">
+        <v>0.982468</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>1.065496</v>
+        <v>2.371927</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -19019,7 +19015,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Accretion of notes receivable 5</t>
+          <t>Current income tax expense</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -19048,22 +19044,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J151" s="5" t="n">
-        <v>-0.313434</v>
-      </c>
-      <c r="K151" s="5" t="n">
-        <v>-0.558178</v>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M151" s="5" t="n">
-        <v>-0.10975</v>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N151" s="5" t="n">
-        <v>-0.199221</v>
+        <v>1.065496</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -19094,7 +19096,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Fair value adjustment of note receivable 5</t>
+          <t>Accretion of notes receivable 5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -19124,12 +19126,10 @@
         </is>
       </c>
       <c r="J152" s="5" t="n">
-        <v>0.441048</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.313434</v>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>-0.558178</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -19137,12 +19137,10 @@
         </is>
       </c>
       <c r="M152" s="5" t="n">
-        <v>0.236471</v>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.10975</v>
+      </c>
+      <c r="N152" s="5" t="n">
+        <v>-0.199221</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
@@ -19173,7 +19171,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities 4</t>
+          <t>Fair value adjustment of note receivable 5</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -19202,10 +19200,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J153" s="5" t="n">
+        <v>0.441048</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -19218,10 +19214,12 @@
         </is>
       </c>
       <c r="M153" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N153" s="5" t="n">
-        <v>0.849405</v>
+        <v>0.236471</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O153" t="inlineStr">
         <is>
@@ -19252,7 +19250,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Loss on disposal of property 6</t>
+          <t>Unrealized loss on marketable securities 4</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -19296,13 +19294,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M154" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="N154" s="5" t="n">
-        <v>0.453577</v>
+        <v>0.849405</v>
       </c>
       <c r="O154" t="inlineStr">
         <is>
@@ -19333,7 +19329,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Interest income and other</t>
+          <t>Loss on disposal of property 6</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
@@ -19372,14 +19368,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L155" s="5" t="n">
-        <v>-0.00182</v>
-      </c>
-      <c r="M155" s="5" t="n">
-        <v>-0.110393</v>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N155" s="5" t="n">
-        <v>-0.081646</v>
+        <v>0.453577</v>
       </c>
       <c r="O155" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange gain 6</t>
+          <t>Interest income and other</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -19449,16 +19449,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L156" s="5" t="n">
+        <v>-0.00182</v>
       </c>
       <c r="M156" s="5" t="n">
-        <v>1.351957</v>
+        <v>-0.110393</v>
       </c>
       <c r="N156" s="5" t="n">
-        <v>-0.748851</v>
+        <v>-0.081646</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -19489,14 +19487,10 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital 9</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Unrealized foreign exchange gain 6</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -19532,14 +19526,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L157" s="5" t="n">
-        <v>0.133609</v>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M157" s="5" t="n">
-        <v>-0.006115</v>
+        <v>1.351957</v>
       </c>
       <c r="N157" s="5" t="n">
-        <v>-0.26587</v>
+        <v>-0.748851</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -19565,17 +19561,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>INVESTING</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 6</t>
+          <t>Change in non-cash working capital 9</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangeInWorkingCapital</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -19613,16 +19609,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L158" s="5" t="n">
+        <v>0.133609</v>
       </c>
       <c r="M158" s="5" t="n">
-        <v>-1.548287</v>
+        <v>-0.006115</v>
       </c>
       <c r="N158" s="5" t="n">
-        <v>-8.075322</v>
+        <v>-0.26587</v>
       </c>
       <c r="O158" t="inlineStr">
         <is>
@@ -19653,12 +19647,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Purchase of investments</t>
+          <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PurchaseOfInvestment</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -19702,10 +19696,10 @@
         </is>
       </c>
       <c r="M159" s="5" t="n">
-        <v>-19.7389</v>
+        <v>-1.548287</v>
       </c>
       <c r="N159" s="5" t="n">
-        <v>4e-06</v>
+        <v>-8.075322</v>
       </c>
       <c r="O159" t="inlineStr">
         <is>
@@ -19736,10 +19730,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Property acquisition 6</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Purchase of investments</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -19781,10 +19779,10 @@
         </is>
       </c>
       <c r="M160" s="5" t="n">
-        <v>-0.124617</v>
+        <v>-19.7389</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>-0.650039</v>
+        <v>4e-06</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
@@ -19815,7 +19813,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Option payments received 6</t>
+          <t>Property acquisition 6</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -19859,13 +19857,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M161" s="5" t="n">
+        <v>-0.124617</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>0.4</v>
+        <v>-0.650039</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -19891,19 +19887,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>INVESTING</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Issuance of common shares 7</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Option payments received 6</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -19929,20 +19921,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J162" s="5" t="n">
-        <v>4.176113</v>
-      </c>
-      <c r="K162" s="5" t="n">
-        <v>0.016667</v>
-      </c>
-      <c r="L162" s="5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M162" s="5" t="n">
-        <v>8.321870000000001</v>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N162" s="5" t="n">
-        <v>34.952999</v>
+        <v>0.4</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -19973,12 +19973,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Share issue costs 7</t>
+          <t>Issuance of common shares 7</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -20006,26 +20006,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J163" s="5" t="n">
+        <v>4.176113</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>0.016667</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>1.5</v>
       </c>
       <c r="M163" s="5" t="n">
-        <v>-0.536277</v>
+        <v>8.321870000000001</v>
       </c>
       <c r="N163" s="5" t="n">
-        <v>-1.743499</v>
+        <v>34.952999</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -20056,10 +20050,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Exercised Unit and broker warrants 7</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Share issue costs 7</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -20101,10 +20099,10 @@
         </is>
       </c>
       <c r="M164" s="5" t="n">
-        <v>2.207113</v>
+        <v>-0.536277</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>5.220188</v>
+        <v>-1.743499</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -20135,7 +20133,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Exercised stock options 7</t>
+          <t>Exercised Unit and broker warrants 7</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -20180,10 +20178,10 @@
         </is>
       </c>
       <c r="M165" s="5" t="n">
-        <v>0.08583300000000001</v>
+        <v>2.207113</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>0.40625</v>
+        <v>5.220188</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -20214,7 +20212,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Note receivable - payment 5</t>
+          <t>Exercised stock options 7</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -20259,12 +20257,10 @@
         </is>
       </c>
       <c r="M166" s="5" t="n">
-        <v>0.09218700000000001</v>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08583300000000001</v>
+      </c>
+      <c r="N166" s="5" t="n">
+        <v>0.40625</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -20295,14 +20291,10 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Increase in cash and cash equivalents</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Note receivable - payment 5</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -20338,14 +20330,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L167" s="5" t="n">
-        <v>0.429894</v>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" s="5" t="n">
-        <v>6.3657</v>
-      </c>
-      <c r="N167" s="5" t="n">
-        <v>10.005958</v>
+        <v>0.09218700000000001</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -20371,15 +20367,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Increase in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -20390,11 +20390,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G168" s="5" t="n">
-        <v>-0.002474</v>
-      </c>
-      <c r="H168" s="5" t="n">
-        <v>0.000485</v>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -20406,19 +20410,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K168" s="5" t="n">
-        <v>0.806565</v>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L168" s="5" t="n">
-        <v>0.099261</v>
+        <v>0.429894</v>
       </c>
       <c r="M168" s="5" t="n">
-        <v>-0.319283</v>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.3657</v>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>10.005958</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -20449,7 +20453,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Accretion of notes receivable 4</t>
+          <t>Foreign exchange translation adjustment</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -20463,15 +20467,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G169" s="5" t="n">
+        <v>-0.002474</v>
+      </c>
+      <c r="H169" s="5" t="n">
+        <v>0.000485</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -20484,15 +20484,13 @@
         </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>-0.558178</v>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.806565</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>0.099261</v>
       </c>
       <c r="M169" s="5" t="n">
-        <v>-0.10975</v>
+        <v>-0.319283</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
@@ -20528,7 +20526,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Fair value adjustment of note receivable 4</t>
+          <t>Accretion of notes receivable 4</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -20562,10 +20560,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K170" s="5" t="n">
+        <v>-0.558178</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -20573,7 +20569,7 @@
         </is>
       </c>
       <c r="M170" s="5" t="n">
-        <v>0.236471</v>
+        <v>-0.10975</v>
       </c>
       <c r="N170" t="inlineStr">
         <is>
@@ -20609,7 +20605,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Loss on marketable security 4</t>
+          <t>Fair value adjustment of note receivable 4</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -20654,7 +20650,7 @@
         </is>
       </c>
       <c r="M171" s="5" t="n">
-        <v>0.025</v>
+        <v>0.236471</v>
       </c>
       <c r="N171" t="inlineStr">
         <is>
@@ -20690,7 +20686,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Unrealized foreign exchange loss 6</t>
+          <t>Loss on marketable security 4</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -20735,7 +20731,7 @@
         </is>
       </c>
       <c r="M172" s="5" t="n">
-        <v>1.351957</v>
+        <v>0.025</v>
       </c>
       <c r="N172" t="inlineStr">
         <is>
@@ -20766,19 +20762,15 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>INVESTING</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Paid exploration and evaluation expenditures 6</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Unrealized foreign exchange loss 6</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -20804,17 +20796,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J173" s="5" t="n">
-        <v>-3.21546</v>
-      </c>
-      <c r="K173" s="5" t="n">
-        <v>-1.336159</v>
-      </c>
-      <c r="L173" s="5" t="n">
-        <v>-0.663834</v>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M173" s="5" t="n">
-        <v>-1.548287</v>
+        <v>1.351957</v>
       </c>
       <c r="N173" t="inlineStr">
         <is>
@@ -20850,10 +20848,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Option payment</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
+          <t>Paid exploration and evaluation expenditures 6</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -20879,23 +20881,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J174" s="5" t="n">
+        <v>-3.21546</v>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>-1.336159</v>
       </c>
       <c r="L174" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.663834</v>
+      </c>
+      <c r="M174" s="5" t="n">
+        <v>-1.548287</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -20931,7 +20927,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Working capital related to investing activities 8</t>
+          <t>Option payment</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -20970,13 +20966,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="5" t="n">
-        <v>0.128385</v>
+      <c r="L175" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
@@ -21007,19 +21003,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>INVESTING</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Issuance of common shares 8</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Working capital related to investing activities 8</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -21055,11 +21047,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L176" s="5" t="n">
-        <v>1.534311</v>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M176" s="5" t="n">
-        <v>8.321870000000001</v>
+        <v>0.128385</v>
       </c>
       <c r="N176" t="inlineStr">
         <is>
@@ -21095,12 +21089,12 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Issuance of common shares 8</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -21128,8 +21122,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J177" s="5" t="n">
-        <v>-0.30998</v>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -21137,10 +21133,10 @@
         </is>
       </c>
       <c r="L177" s="5" t="n">
-        <v>-0.123385</v>
+        <v>1.534311</v>
       </c>
       <c r="M177" s="5" t="n">
-        <v>-0.536277</v>
+        <v>8.321870000000001</v>
       </c>
       <c r="N177" t="inlineStr">
         <is>
@@ -21176,10 +21172,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Exercised Unit and broker warrants</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -21205,23 +21205,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J178" s="5" t="n">
+        <v>-0.30998</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L178" s="5" t="n">
+        <v>-0.123385</v>
       </c>
       <c r="M178" s="5" t="n">
-        <v>2.207113</v>
+        <v>-0.536277</v>
       </c>
       <c r="N178" t="inlineStr">
         <is>
@@ -21257,7 +21253,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Exercised stock options</t>
+          <t>Exercised Unit and broker warrants</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -21302,7 +21298,7 @@
         </is>
       </c>
       <c r="M179" s="5" t="n">
-        <v>0.08583300000000001</v>
+        <v>2.207113</v>
       </c>
       <c r="N179" t="inlineStr">
         <is>
@@ -21338,7 +21334,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Note receivable - payment</t>
+          <t>Exercised stock options</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -21383,7 +21379,7 @@
         </is>
       </c>
       <c r="M180" s="5" t="n">
-        <v>0.09218700000000001</v>
+        <v>0.08583300000000001</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -21414,12 +21410,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents is comprised of</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Term deposits</t>
+          <t>Note receivable - payment</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -21443,11 +21439,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I181" s="5" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="J181" s="5" t="n">
-        <v>2.01632</v>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         </is>
       </c>
       <c r="M181" s="5" t="n">
-        <v>4.030617</v>
+        <v>0.09218700000000001</v>
       </c>
       <c r="N181" t="inlineStr">
         <is>
@@ -21491,12 +21491,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>Cash and cash equivalents is comprised of</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Impairment of notes receivable 4</t>
+          <t>Term deposits</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -21520,28 +21520,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K182" s="5" t="n">
-        <v>1.516424</v>
+      <c r="I182" s="5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>2.01632</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M182" s="5" t="n">
+        <v>4.030617</v>
       </c>
       <c r="N182" t="inlineStr">
         <is>
@@ -21577,14 +21573,10 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Share-based compensation 6</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Impairment of notes receivable 4</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -21616,7 +21608,7 @@
         </is>
       </c>
       <c r="K183" s="5" t="n">
-        <v>0.386527</v>
+        <v>1.516424</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -21662,10 +21654,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
+          <t>Share-based compensation 6</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -21691,14 +21687,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J184" s="5" t="n">
-        <v>-0.050884</v>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K184" s="5" t="n">
-        <v>-0.07566199999999999</v>
-      </c>
-      <c r="L184" s="5" t="n">
-        <v>-0.00182</v>
+        <v>0.386527</v>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Foreign exchange gain 4</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -21768,18 +21768,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J185" s="5" t="n">
+        <v>-0.050884</v>
       </c>
       <c r="K185" s="5" t="n">
-        <v>-0.06197</v>
-      </c>
-      <c r="L185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.07566199999999999</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>-0.00182</v>
       </c>
       <c r="M185" t="inlineStr">
         <is>
@@ -21820,14 +21816,10 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Receivables</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain 4</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -21848,17 +21840,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I186" s="5" t="n">
-        <v>-0.01665</v>
-      </c>
-      <c r="J186" s="5" t="n">
-        <v>-0.035132</v>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K186" s="5" t="n">
-        <v>0.052678</v>
-      </c>
-      <c r="L186" s="5" t="n">
-        <v>-0.006143</v>
+        <v>-0.06197</v>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -21899,12 +21897,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Trade and other payables</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -21917,23 +21915,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" s="5" t="n">
-        <v>0.033502</v>
-      </c>
-      <c r="H187" s="5" t="n">
-        <v>0.05295</v>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" s="5" t="n">
-        <v>0.082469</v>
+        <v>-0.01665</v>
       </c>
       <c r="J187" s="5" t="n">
-        <v>-0.213376</v>
+        <v>-0.035132</v>
       </c>
       <c r="K187" s="5" t="n">
-        <v>-0.010747</v>
+        <v>0.052678</v>
       </c>
       <c r="L187" s="5" t="n">
-        <v>0.152631</v>
+        <v>-0.006143</v>
       </c>
       <c r="M187" t="inlineStr">
         <is>
@@ -21974,12 +21976,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Trade and other payables</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -21992,27 +21994,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G188" s="5" t="n">
+        <v>0.033502</v>
+      </c>
+      <c r="H188" s="5" t="n">
+        <v>0.05295</v>
       </c>
       <c r="I188" s="5" t="n">
-        <v>-0.072661</v>
+        <v>0.082469</v>
       </c>
       <c r="J188" s="5" t="n">
-        <v>-0.015072</v>
+        <v>-0.213376</v>
       </c>
       <c r="K188" s="5" t="n">
-        <v>0.07852199999999999</v>
+        <v>-0.010747</v>
       </c>
       <c r="L188" s="5" t="n">
-        <v>-0.012879</v>
+        <v>0.152631</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -22048,15 +22046,19 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>INVESTING</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Working capital related to investing activities</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -22077,21 +22079,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I189" s="5" t="n">
+        <v>-0.072661</v>
       </c>
       <c r="J189" s="5" t="n">
-        <v>-0.208241</v>
+        <v>-0.015072</v>
       </c>
       <c r="K189" s="5" t="n">
-        <v>-0.13946</v>
-      </c>
-      <c r="L189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07852199999999999</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>-0.012879</v>
       </c>
       <c r="M189" t="inlineStr">
         <is>
@@ -22132,7 +22130,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Collection of loan receivable</t>
+          <t>Working capital related to investing activities</t>
         </is>
       </c>
       <c r="D190" t="inlineStr"/>
@@ -22161,13 +22159,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J190" s="5" t="n">
+        <v>-0.208241</v>
       </c>
       <c r="K190" s="5" t="n">
-        <v>0.006545</v>
+        <v>-0.13946</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -22208,12 +22204,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>FINANCING</t>
+          <t>INVESTING</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Exercised warrants</t>
+          <t>Collection of loan receivable</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -22247,13 +22243,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L191" s="5" t="n">
-        <v>0.034311</v>
+      <c r="K191" s="5" t="n">
+        <v>0.006545</v>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
@@ -22294,7 +22290,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Recovered costs incurred in CGS properties</t>
+          <t>Exercised warrants</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -22328,13 +22324,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K192" s="5" t="n">
-        <v>-0.028675</v>
-      </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>0.034311</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -22375,14 +22371,10 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cash flow provided by (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Recovered costs incurred in CGS properties</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -22408,14 +22400,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J193" s="5" t="n">
-        <v>3.866132</v>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K193" s="5" t="n">
-        <v>-0.012008</v>
-      </c>
-      <c r="L193" s="5" t="n">
-        <v>1.410926</v>
+        <v>-0.028675</v>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -22456,12 +22452,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents</t>
+          <t>Cash flow provided by (used in) financing activities</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -22490,13 +22486,13 @@
         </is>
       </c>
       <c r="J194" s="5" t="n">
-        <v>-4.161951</v>
+        <v>3.866132</v>
       </c>
       <c r="K194" s="5" t="n">
-        <v>-2.427874</v>
+        <v>-0.012008</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>0.429894</v>
+        <v>1.410926</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -22537,10 +22533,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents and term deposits, beginning of year</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Decrease in cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -22567,13 +22567,13 @@
         </is>
       </c>
       <c r="J195" s="5" t="n">
-        <v>6.72827</v>
+        <v>-4.161951</v>
       </c>
       <c r="K195" s="5" t="n">
-        <v>2.566319</v>
+        <v>-2.427874</v>
       </c>
       <c r="L195" s="5" t="n">
-        <v>0.138445</v>
+        <v>0.429894</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -22609,12 +22609,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>FINANCING</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Impairment of notes receivable 5</t>
+          <t>Cash and cash equivalents and term deposits, beginning of year</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -22643,18 +22643,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J196" s="5" t="n">
+        <v>6.72827</v>
       </c>
       <c r="K196" s="5" t="n">
-        <v>1.516424</v>
-      </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.566319</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>0.138445</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -22695,14 +22691,10 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based compensation 7</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Impairment of notes receivable 5</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -22728,11 +22720,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J197" s="5" t="n">
-        <v>0.696801</v>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K197" s="5" t="n">
-        <v>0.386527</v>
+        <v>1.516424</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -22778,10 +22772,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Recovery of transaction costs 4</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>Share-based compensation 7</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -22808,12 +22806,10 @@
         </is>
       </c>
       <c r="J198" s="5" t="n">
-        <v>-0.065</v>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.696801</v>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>0.386527</v>
       </c>
       <c r="L198" t="inlineStr">
         <is>
@@ -22859,7 +22855,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Foreign exchange gain 5</t>
+          <t>Recovery of transaction costs 4</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -22889,10 +22885,12 @@
         </is>
       </c>
       <c r="J199" s="5" t="n">
-        <v>-0.226241</v>
-      </c>
-      <c r="K199" s="5" t="n">
-        <v>-0.06197</v>
+        <v>-0.065</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -22933,12 +22931,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>INVESTING</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Advances of notes receivable 5</t>
+          <t>Foreign exchange gain 5</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -22968,12 +22966,10 @@
         </is>
       </c>
       <c r="J200" s="5" t="n">
-        <v>-1.456837</v>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.226241</v>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>-0.06197</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -23014,19 +23010,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>INVESTING</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Advances of notes receivable 5</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -23047,11 +23039,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I201" s="5" t="n">
-        <v>-1.023662</v>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J201" s="5" t="n">
-        <v>-3.366255</v>
+        <v>-1.456837</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
@@ -23097,21 +23091,23 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Net and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E202" s="5" t="n">
-        <v>0.0175</v>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -23129,10 +23125,10 @@
         </is>
       </c>
       <c r="I202" s="5" t="n">
-        <v>0.465149</v>
+        <v>-1.023662</v>
       </c>
       <c r="J202" s="5" t="n">
-        <v>0.696801</v>
+        <v>-3.366255</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
@@ -23183,14 +23179,16 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Accretion of note receivable 5</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -23207,13 +23205,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I203" s="5" t="n">
+        <v>0.465149</v>
       </c>
       <c r="J203" s="5" t="n">
-        <v>-0.313434</v>
+        <v>0.696801</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
@@ -23264,7 +23260,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Accretion of note receivable 5</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -23294,7 +23290,7 @@
         </is>
       </c>
       <c r="J204" s="5" t="n">
-        <v>-0.226241</v>
+        <v>-0.313434</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
@@ -23340,19 +23336,15 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Capitalized share-based compensation</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -23373,13 +23365,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I205" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>-0.226241</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -23430,10 +23422,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Loan and advances to Kairos Metals Corp. 4</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>Capitalized share-based compensation</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -23454,13 +23450,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J206" s="5" t="n">
-        <v>-1.456837</v>
+      <c r="I206" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -23511,7 +23507,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (2,478,714) -</t>
+          <t>Loan and advances to Kairos Metals Corp. 4</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -23535,11 +23531,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I207" s="5" t="n">
-        <v>-1.045556</v>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J207" s="5" t="n">
-        <v>-3.21546</v>
+        <v>-1.456837</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -23590,7 +23588,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Working capital related to investing activities -</t>
+          <t>Exploration and evaluation expenditures (2,478,714) -</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -23615,10 +23613,10 @@
         </is>
       </c>
       <c r="I208" s="5" t="n">
-        <v>0.054429</v>
+        <v>-1.045556</v>
       </c>
       <c r="J208" s="5" t="n">
-        <v>-0.208241</v>
+        <v>-3.21546</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -23669,7 +23667,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Cash flow used in investing activities (2,478,714)</t>
+          <t>Working capital related to investing activities -</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -23694,10 +23692,10 @@
         </is>
       </c>
       <c r="I209" s="5" t="n">
-        <v>-0.891127</v>
+        <v>0.054429</v>
       </c>
       <c r="J209" s="5" t="n">
-        <v>-4.880538</v>
+        <v>-0.208241</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
@@ -23743,12 +23741,12 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS USED IN INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Repayment of debentures</t>
+          <t>Cash flow used in investing activities (2,478,714)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -23767,16 +23765,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H210" s="5" t="n">
-        <v>0.4</v>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I210" s="5" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.891127</v>
+      </c>
+      <c r="J210" s="5" t="n">
+        <v>-4.880538</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -23827,14 +23825,10 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Issuance of common shares 7(b) - -</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>CommonStockIssuance</t>
-        </is>
-      </c>
+          <t>Repayment of debentures</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
@@ -23850,16 +23844,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>0.4</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>9.590662999999999</v>
-      </c>
-      <c r="J211" s="5" t="n">
-        <v>4.176113</v>
+        <v>-0.4</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -23910,12 +23904,12 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Issuance of common shares 7(b) - -</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -23939,10 +23933,10 @@
         </is>
       </c>
       <c r="I212" s="5" t="n">
-        <v>-0.690267</v>
+        <v>9.590662999999999</v>
       </c>
       <c r="J212" s="5" t="n">
-        <v>-0.309981</v>
+        <v>4.176113</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -23993,10 +23987,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Repayment to director</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -24018,12 +24016,10 @@
         </is>
       </c>
       <c r="I213" s="5" t="n">
-        <v>-0.349338</v>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.690267</v>
+      </c>
+      <c r="J213" s="5" t="n">
+        <v>-0.309981</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -24074,7 +24070,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Note receivable</t>
+          <t>Repayment to director</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -24099,7 +24095,7 @@
         </is>
       </c>
       <c r="I214" s="5" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.349338</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -24155,14 +24151,10 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Cash flow provided by financing activities - -</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Note receivable</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -24184,10 +24176,12 @@
         </is>
       </c>
       <c r="I215" s="5" t="n">
-        <v>8.057858</v>
-      </c>
-      <c r="J215" s="5" t="n">
-        <v>3.866132</v>
+        <v>-0.09320000000000001</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -24238,12 +24232,12 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash -</t>
+          <t>Cash flow provided by financing activities - -</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -24267,10 +24261,10 @@
         </is>
       </c>
       <c r="I216" s="5" t="n">
-        <v>6.601376</v>
+        <v>8.057858</v>
       </c>
       <c r="J216" s="5" t="n">
-        <v>-4.161951</v>
+        <v>3.866132</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -24321,12 +24315,12 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year 310,382</t>
+          <t>Increase (decrease) in cash -</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -24350,10 +24344,10 @@
         </is>
       </c>
       <c r="I217" s="5" t="n">
-        <v>0.126894</v>
+        <v>6.601376</v>
       </c>
       <c r="J217" s="5" t="n">
-        <v>6.72827</v>
+        <v>-4.161951</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -24404,12 +24398,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of the year $ 310,382 $</t>
+          <t>Cash, beginning of the year 310,382</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -24433,10 +24427,10 @@
         </is>
       </c>
       <c r="I218" s="5" t="n">
+        <v>0.126894</v>
+      </c>
+      <c r="J218" s="5" t="n">
         <v>6.72827</v>
-      </c>
-      <c r="J218" s="5" t="n">
-        <v>2.566319</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -24482,15 +24476,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents is comprised of</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Interest paid during the period $</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of the year $ 310,382 $</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -24512,12 +24510,10 @@
         </is>
       </c>
       <c r="I219" s="5" t="n">
-        <v>0.012295</v>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.72827</v>
+      </c>
+      <c r="J219" s="5" t="n">
+        <v>2.566319</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -24568,7 +24564,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Interest received in the period $</t>
+          <t>Interest paid during the period $</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -24593,10 +24589,12 @@
         </is>
       </c>
       <c r="I220" s="5" t="n">
-        <v>0.007643</v>
-      </c>
-      <c r="J220" s="5" t="n">
-        <v>0.047496</v>
+        <v>0.012295</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -24642,19 +24640,15 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Cash and cash equivalents is comprised of</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Interest received in the period $</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -24670,16 +24664,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" s="5" t="n">
-        <v>-0.08164399999999999</v>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I221" s="5" t="n">
-        <v>-1.023662</v>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007643</v>
+      </c>
+      <c r="J221" s="5" t="n">
+        <v>0.047496</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -24725,17 +24719,17 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Other receivables</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -24754,10 +24748,10 @@
         </is>
       </c>
       <c r="H222" s="5" t="n">
-        <v>-0.002196</v>
+        <v>-0.08164399999999999</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>-0.01665</v>
+        <v>-1.023662</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -24808,17 +24802,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (308,810) -</t>
+          <t>Other receivables</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -24837,10 +24831,10 @@
         </is>
       </c>
       <c r="H223" s="5" t="n">
-        <v>-0.60494</v>
+        <v>-0.002196</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>-1.045556</v>
+        <v>-0.01665</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -24896,12 +24890,12 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Capitalized share-based compensation</t>
+          <t>Exploration and evaluation expenditures (308,810) -</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -24919,13 +24913,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>-0.60494</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>0.1</v>
+        <v>-1.045556</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -24981,26 +24973,36 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Working capital related to investing activities -</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
+          <t>Capitalized share-based compensation</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F225" s="5" t="n">
-        <v>0.000956</v>
-      </c>
-      <c r="G225" s="5" t="n">
-        <v>-0.0476</v>
-      </c>
-      <c r="H225" s="5" t="n">
-        <v>0.055786</v>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I225" s="5" t="n">
-        <v>0.054429</v>
+        <v>0.1</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -25056,7 +25058,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Cash flow used in investing activities (308,810)</t>
+          <t>Working capital related to investing activities -</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -25065,21 +25067,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F226" s="5" t="n">
+        <v>0.000956</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="H226" s="5" t="n">
-        <v>-0.549154</v>
+        <v>0.055786</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>-0.891127</v>
+        <v>0.054429</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -25130,12 +25128,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Issuance of share capital - - 7(b)</t>
+          <t>Cash flow used in investing activities (308,810)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -25154,13 +25152,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H227" s="5" t="n">
+        <v>-0.549154</v>
       </c>
       <c r="I227" s="5" t="n">
-        <v>9.5206</v>
+        <v>-0.891127</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -25211,12 +25207,12 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Exercised warrants                                                                                           70,063</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Note receivable 4</t>
+          <t>Issuance of share capital - - 7(b)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr"/>
@@ -25241,7 +25237,7 @@
         </is>
       </c>
       <c r="I228" s="5" t="n">
-        <v>-0.09320000000000001</v>
+        <v>9.5206</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -25297,7 +25293,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Share issue costs - - 7(b,c)</t>
+          <t>Note receivable 4</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -25322,7 +25318,7 @@
         </is>
       </c>
       <c r="I229" s="5" t="n">
-        <v>-0.690267</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -25378,7 +25374,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Advances from director, net of repayments</t>
+          <t>Share issue costs - - 7(b,c)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
@@ -25397,11 +25393,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H230" s="5" t="n">
-        <v>0.303591</v>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I230" s="5" t="n">
-        <v>-0.349338</v>
+        <v>-0.690267</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -25457,14 +25455,10 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Cash flow provided by financing activities - -</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Advances from director, net of repayments</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -25481,10 +25475,10 @@
         </is>
       </c>
       <c r="H231" s="5" t="n">
-        <v>0.703591</v>
+        <v>0.303591</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>8.057858</v>
+        <v>-0.349338</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -25540,12 +25534,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Increase in cash -</t>
+          <t>Cash flow provided by financing activities - -</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -25564,10 +25558,10 @@
         </is>
       </c>
       <c r="H232" s="5" t="n">
-        <v>0.124032</v>
+        <v>0.703591</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>6.601376</v>
+        <v>8.057858</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -25623,12 +25617,12 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 310,382</t>
+          <t>Increase in cash -</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -25647,10 +25641,10 @@
         </is>
       </c>
       <c r="H233" s="5" t="n">
-        <v>0.002862</v>
+        <v>0.124032</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>0.126894</v>
+        <v>6.601376</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -25706,12 +25700,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $ 310,382 $</t>
+          <t>Cash, beginning of year 310,382</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -25730,10 +25724,10 @@
         </is>
       </c>
       <c r="H234" s="5" t="n">
+        <v>0.002862</v>
+      </c>
+      <c r="I234" s="5" t="n">
         <v>0.126894</v>
-      </c>
-      <c r="I234" s="5" t="n">
-        <v>6.72827</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -25784,15 +25778,19 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents is comprised of</t>
+          <t>Exercised warrants                                                                                           70,063</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Interest paid in the year $</t>
-        </is>
-      </c>
-      <c r="D235" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $ 310,382 $</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -25809,10 +25807,10 @@
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>0.004511</v>
+        <v>0.126894</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>0.012295</v>
+        <v>6.72827</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -25863,12 +25861,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>Cash and cash equivalents is comprised of</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year #REF! $ 8,482 $</t>
+          <t>Interest paid in the year $</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
@@ -25882,16 +25880,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G236" s="5" t="n">
-        <v>-0.037383</v>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H236" s="5" t="n">
-        <v>-0.08164399999999999</v>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004511</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>0.012295</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -25942,12 +25940,12 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>GST receivable</t>
+          <t>Comprehensive loss for the year #REF! $ 8,482 $</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
@@ -25962,10 +25960,10 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>-0.002395</v>
+        <v>-0.037383</v>
       </c>
       <c r="H237" s="5" t="n">
-        <v>-0.002196</v>
+        <v>-0.08164399999999999</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -26026,10 +26024,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Cash used in operating activities #REF! #REF!</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr"/>
+          <t>GST receivable</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -26041,10 +26043,10 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>-0.008750000000000001</v>
+        <v>-0.002395</v>
       </c>
       <c r="H238" s="5" t="n">
-        <v>-0.030405</v>
+        <v>-0.002196</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -26100,19 +26102,15 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 131,806 -</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Cash used in operating activities #REF! #REF!</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -26124,10 +26122,10 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>-0.25417</v>
+        <v>-0.008750000000000001</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>-0.60494</v>
+        <v>-0.030405</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -26188,12 +26186,12 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Cash used in investing activities 131,806</t>
+          <t>Exploration and evaluation expenditures 131,806 -</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -26207,10 +26205,10 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>-0.30177</v>
+        <v>-0.25417</v>
       </c>
       <c r="H240" s="5" t="n">
-        <v>-0.549154</v>
+        <v>-0.60494</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -26266,15 +26264,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Proceeds from debentures</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
+          <t>Cash used in investing activities 131,806</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -26285,13 +26287,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G241" s="5" t="n">
+        <v>-0.30177</v>
       </c>
       <c r="H241" s="5" t="n">
-        <v>0.4</v>
+        <v>-0.549154</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Issuance of share capital (note 6(b)) - -</t>
+          <t>Proceeds from debentures</t>
         </is>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -26366,13 +26366,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G242" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H242" s="5" t="n">
+        <v>0.4</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Advances from director (net of repayments)</t>
+          <t>Issuance of share capital (note 6(b)) - -</t>
         </is>
       </c>
       <c r="D243" t="inlineStr"/>
@@ -26448,10 +26448,12 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>-0.188697</v>
-      </c>
-      <c r="H243" s="5" t="n">
-        <v>0.303591</v>
+        <v>0.5</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -26512,14 +26514,10 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Cash from financing activities - -</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Advances from director (net of repayments)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -26531,10 +26529,10 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>0.311303</v>
+        <v>-0.188697</v>
       </c>
       <c r="H244" s="5" t="n">
-        <v>0.703591</v>
+        <v>0.303591</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -26595,10 +26593,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Increase in cash #REF!</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr"/>
+          <t>Cash from financing activities - -</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -26610,10 +26612,10 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>0.000783</v>
+        <v>0.311303</v>
       </c>
       <c r="H245" s="5" t="n">
-        <v>0.124032</v>
+        <v>0.703591</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -26674,27 +26676,25 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Cash, beginning of year 310,382</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Increase in cash #REF!</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F246" s="5" t="n">
-        <v>0.103</v>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>0.002079</v>
+        <v>0.000783</v>
       </c>
       <c r="H246" s="5" t="n">
-        <v>0.002862</v>
+        <v>0.124032</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -26755,23 +26755,27 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Cash, end of year #REF! $</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Cash, beginning of year 310,382</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F247" s="5" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="G247" s="5" t="n">
         <v>0.002079</v>
       </c>
-      <c r="G247" s="5" t="n">
+      <c r="H247" s="5" t="n">
         <v>0.002862</v>
-      </c>
-      <c r="H247" s="5" t="n">
-        <v>0.126894</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -26827,12 +26831,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Net loss for the period $ (14,737) $ (6,451) $</t>
+          <t>Cash, end of year #REF! $</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -26842,15 +26846,13 @@
         </is>
       </c>
       <c r="F248" s="5" t="n">
-        <v>-0.052316</v>
+        <v>0.002079</v>
       </c>
       <c r="G248" s="5" t="n">
-        <v>-0.039857</v>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002862</v>
+      </c>
+      <c r="H248" s="5" t="n">
+        <v>0.126894</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -26906,29 +26908,25 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items 17,590</t>
-        </is>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Net loss for the period $ (14,737) $ (6,451) $</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F249" s="5" t="n">
-        <v>0.007998999999999999</v>
+        <v>-0.052316</v>
       </c>
       <c r="G249" s="5" t="n">
-        <v>0.031107</v>
+        <v>-0.039857</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -26994,20 +26992,24 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Cash used in operating activities (14,737) #REF!</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Changes in non-cash working capital items 17,590</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F250" s="5" t="n">
-        <v>-0.044317</v>
+        <v>0.007998999999999999</v>
       </c>
       <c r="G250" s="5" t="n">
-        <v>-0.008750000000000001</v>
+        <v>0.031107</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -27068,29 +27070,25 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 482,576 -</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Cash used in operating activities (14,737) #REF!</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F251" s="5" t="n">
-        <v>-0.214477</v>
+        <v>-0.044317</v>
       </c>
       <c r="G251" s="5" t="n">
-        <v>-0.25417</v>
+        <v>-0.008750000000000001</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -27156,12 +27154,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cash used in investing activities 482,576</t>
+          <t>Exploration and evaluation expenditures 482,576 -</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -27170,10 +27168,10 @@
         </is>
       </c>
       <c r="F252" s="5" t="n">
-        <v>-0.213521</v>
+        <v>-0.214477</v>
       </c>
       <c r="G252" s="5" t="n">
-        <v>-0.30177</v>
+        <v>-0.25417</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -27234,27 +27232,29 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Issuance of share capital (note 5(b)) - -</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr"/>
+          <t>Cash used in investing activities 482,576</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F253" s="5" t="n">
+        <v>-0.213521</v>
       </c>
       <c r="G253" s="5" t="n">
-        <v>0.5</v>
+        <v>-0.30177</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Advances from director (repaid)</t>
+          <t>Issuance of share capital (note 5(b)) - -</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
@@ -27329,11 +27329,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F254" s="5" t="n">
-        <v>0.156917</v>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>-0.188697</v>
+        <v>0.5</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -27399,7 +27401,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Cash from financing activities 145,488 -</t>
+          <t>Advances from director (repaid)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -27412,7 +27414,7 @@
         <v>0.156917</v>
       </c>
       <c r="G255" s="5" t="n">
-        <v>0.311303</v>
+        <v>-0.188697</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -27478,24 +27480,20 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash #REF!</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash from financing activities 145,488 -</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-0.100921</v>
+        <v>0.156917</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>0.000783</v>
+        <v>0.311303</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -27556,25 +27554,29 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Net loss for the period $ 13,080 $ (415,066) $</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" s="5" t="n">
-        <v>-0.460931</v>
+          <t>Increase (decrease) in cash #REF!</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F257" s="5" t="n">
-        <v>-0.052316</v>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.100921</v>
+      </c>
+      <c r="G257" s="5" t="n">
+        <v>0.000783</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -27635,24 +27637,20 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Add (deduct) items not affecting cash flow</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items 9,906</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>ChangeInWorkingCapital</t>
-        </is>
-      </c>
+          <t>Net loss for the period $ 13,080 $ (415,066) $</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
       <c r="E258" s="5" t="n">
-        <v>0.000315</v>
+        <v>-0.460931</v>
       </c>
       <c r="F258" s="5" t="n">
-        <v>0.007998999999999999</v>
+        <v>-0.052316</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -27723,15 +27721,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Cash used in operating activities 13,080 #REF!</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
+          <t>Changes in non-cash working capital items 9,906</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
-        <v>-0.443116</v>
+        <v>0.000315</v>
       </c>
       <c r="F259" s="5" t="n">
-        <v>-0.044317</v>
+        <v>0.007998999999999999</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -27797,24 +27799,20 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Add (deduct) items not affecting cash flow</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 522,269 -</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Cash used in operating activities 13,080 #REF!</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
       <c r="E260" s="5" t="n">
-        <v>-0.634189</v>
+        <v>-0.443116</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>-0.214477</v>
+        <v>-0.044317</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -27885,19 +27883,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Cash used in investing activities 522,269</t>
+          <t>Exploration and evaluation expenditures 522,269 -</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E261" s="5" t="n">
         <v>-0.634189</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>-0.213521</v>
+        <v>-0.214477</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -27963,22 +27961,24 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Issuance of share capital - -</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr"/>
+          <t>Cash used in investing activities 522,269</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.634189</v>
+      </c>
+      <c r="F262" s="5" t="n">
+        <v>-0.213521</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -28049,16 +28049,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Share issue costs - -</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>Issuance of share capital - -</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
       <c r="E263" s="5" t="n">
-        <v>-0.00575</v>
+        <v>0.8</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28134,15 +28130,21 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Advance from director 145,488 -</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
+          <t>Share issue costs - -</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E264" s="5" t="n">
-        <v>0.396313</v>
-      </c>
-      <c r="F264" s="5" t="n">
-        <v>0.156917</v>
+        <v>-0.00575</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -28213,17 +28215,15 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Advances repaid</t>
+          <t>Advance from director 145,488 -</t>
         </is>
       </c>
       <c r="D265" t="inlineStr"/>
       <c r="E265" s="5" t="n">
-        <v>-0.318786</v>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.396313</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>0.156917</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -28294,19 +28294,17 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES total</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Advances repaid</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
       <c r="E266" s="5" t="n">
-        <v>0.871777</v>
-      </c>
-      <c r="F266" s="5" t="n">
-        <v>0.156917</v>
+        <v>-0.318786</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -28377,19 +28375,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Decrease in cash and cash equivalents #REF!</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES total</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">
-        <v>-0.205528</v>
+        <v>0.871777</v>
       </c>
       <c r="F267" s="5" t="n">
-        <v>-0.10092</v>
+        <v>0.156917</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -28460,19 +28458,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of period 310,382</t>
+          <t>Decrease in cash and cash equivalents #REF!</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">
-        <v>0.308528</v>
+        <v>-0.205528</v>
       </c>
       <c r="F268" s="5" t="n">
-        <v>0.103</v>
+        <v>-0.10092</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -28543,19 +28541,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of period #REF! $</t>
+          <t>Cash and cash equivalents, beginning of period 310,382</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E269" s="5" t="n">
+        <v>0.308528</v>
+      </c>
+      <c r="F269" s="5" t="n">
         <v>0.103</v>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>0.002079</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -28626,23 +28624,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Interest and income taxes paid $</t>
+          <t>Cash and cash equivalents, end of period #REF! $</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>IncomeTaxPaidSupplementalData</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>0.002079</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -28703,22 +28697,22 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>General and administrative 10 $</t>
+          <t>Interest and income taxes paid $</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>IncomeTaxPaidSupplementalData</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -28771,11 +28765,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O271" s="5" t="n">
-        <v>3.877406</v>
-      </c>
-      <c r="P271" s="5" t="n">
-        <v>3.390042</v>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q271" t="inlineStr">
         <is>
@@ -28796,12 +28794,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Depreciation 7</t>
+          <t>General and administrative 10 $</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -28855,10 +28853,10 @@
         </is>
       </c>
       <c r="O272" s="5" t="n">
-        <v>0.03557</v>
+        <v>3.877406</v>
       </c>
       <c r="P272" s="5" t="n">
-        <v>0.043148</v>
+        <v>3.390042</v>
       </c>
       <c r="Q272" t="inlineStr">
         <is>
@@ -28879,10 +28877,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties 7</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>Depreciation 7</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -28933,13 +28935,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O273" s="5" t="n">
+        <v>0.03557</v>
       </c>
       <c r="P273" s="5" t="n">
-        <v>14.908213</v>
+        <v>0.043148</v>
       </c>
       <c r="Q273" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Share-based compensation 8(f)</t>
+          <t>Impairment of mineral properties 7</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -29014,11 +29014,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O274" s="5" t="n">
-        <v>3.079847</v>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P274" s="5" t="n">
-        <v>0.23748</v>
+        <v>14.908213</v>
       </c>
       <c r="Q274" t="inlineStr">
         <is>
@@ -29039,14 +29041,10 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation 8(f)</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -29098,10 +29096,10 @@
         </is>
       </c>
       <c r="O275" s="5" t="n">
-        <v>6.992823</v>
+        <v>3.079847</v>
       </c>
       <c r="P275" s="5" t="n">
-        <v>18.578883</v>
+        <v>0.23748</v>
       </c>
       <c r="Q275" t="inlineStr">
         <is>
@@ -29117,15 +29115,19 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Other (income) expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Interest income on cash equivalents and short-term deposits</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr"/>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -29177,10 +29179,10 @@
         </is>
       </c>
       <c r="O276" s="5" t="n">
-        <v>-1.185444</v>
+        <v>6.992823</v>
       </c>
       <c r="P276" s="5" t="n">
-        <v>-0.457917</v>
+        <v>18.578883</v>
       </c>
       <c r="Q276" t="inlineStr">
         <is>
@@ -29201,7 +29203,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Currency gains 11</t>
+          <t>Interest income on cash equivalents and short-term deposits</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -29256,10 +29258,10 @@
         </is>
       </c>
       <c r="O277" s="5" t="n">
-        <v>-2.996778</v>
+        <v>-1.185444</v>
       </c>
       <c r="P277" s="5" t="n">
-        <v>-1.674049</v>
+        <v>-0.457917</v>
       </c>
       <c r="Q277" t="inlineStr">
         <is>
@@ -29280,7 +29282,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Change in net monetary position due to hyperinflation 3(j)</t>
+          <t>Currency gains 11</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -29335,10 +29337,10 @@
         </is>
       </c>
       <c r="O278" s="5" t="n">
-        <v>-4.214396</v>
+        <v>-2.996778</v>
       </c>
       <c r="P278" s="5" t="n">
-        <v>-29.37359</v>
+        <v>-1.674049</v>
       </c>
       <c r="Q278" t="inlineStr">
         <is>
@@ -29359,7 +29361,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Reclassification of accumulated exchange difference on spin-out 4</t>
+          <t>Change in net monetary position due to hyperinflation 3(j)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -29413,13 +29415,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O279" s="5" t="n">
+        <v>-4.214396</v>
       </c>
       <c r="P279" s="5" t="n">
-        <v>0.921058</v>
+        <v>-29.37359</v>
       </c>
       <c r="Q279" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities 5</t>
+          <t>Reclassification of accumulated exchange difference on spin-out 4</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -29494,11 +29494,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O280" s="5" t="n">
-        <v>0.97717</v>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P280" s="5" t="n">
-        <v>0.638771</v>
+        <v>0.921058</v>
       </c>
       <c r="Q280" t="inlineStr">
         <is>
@@ -29519,7 +29521,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Gain on sale of marketable securities 5</t>
+          <t>Unrealized loss on marketable securities 5</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -29573,13 +29575,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O281" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O281" s="5" t="n">
+        <v>0.97717</v>
       </c>
       <c r="P281" s="5" t="n">
-        <v>-0.00281</v>
+        <v>0.638771</v>
       </c>
       <c r="Q281" t="inlineStr">
         <is>
@@ -29600,14 +29600,10 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gain on sale of marketable securities 5</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -29658,11 +29654,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O282" s="5" t="n">
-        <v>0.006495</v>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P282" s="5" t="n">
-        <v>0.001956</v>
+        <v>-0.00281</v>
       </c>
       <c r="Q282" t="inlineStr">
         <is>
@@ -29683,7 +29681,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Total other (income) expenses</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -29742,10 +29740,10 @@
         </is>
       </c>
       <c r="O283" s="5" t="n">
-        <v>-7.412953</v>
+        <v>0.006495</v>
       </c>
       <c r="P283" s="5" t="n">
-        <v>-29.946581</v>
+        <v>0.001956</v>
       </c>
       <c r="Q283" t="inlineStr">
         <is>
@@ -29766,12 +29764,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Income before taxes</t>
+          <t>Total other (income) expenses</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -29825,10 +29823,10 @@
         </is>
       </c>
       <c r="O284" s="5" t="n">
-        <v>0.42013</v>
+        <v>-7.412953</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>11.367698</v>
+        <v>-29.946581</v>
       </c>
       <c r="Q284" t="inlineStr">
         <is>
@@ -29849,10 +29847,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Tax expense (recovery) 12</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr"/>
+          <t>Income before taxes</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -29904,10 +29906,10 @@
         </is>
       </c>
       <c r="O285" s="5" t="n">
-        <v>-0.047452</v>
+        <v>0.42013</v>
       </c>
       <c r="P285" s="5" t="n">
-        <v>2.01951</v>
+        <v>11.367698</v>
       </c>
       <c r="Q285" t="inlineStr">
         <is>
@@ -29928,14 +29930,10 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Net income</t>
-        </is>
-      </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Tax expense (recovery) 12</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -29987,10 +29985,10 @@
         </is>
       </c>
       <c r="O286" s="5" t="n">
-        <v>0.467582</v>
+        <v>-0.047452</v>
       </c>
       <c r="P286" s="5" t="n">
-        <v>9.348188</v>
+        <v>2.01951</v>
       </c>
       <c r="Q286" t="inlineStr">
         <is>
@@ -30006,15 +30004,19 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other (income) expenses</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Exchange differences on translation of subsidiaries</t>
-        </is>
-      </c>
-      <c r="D287" t="inlineStr"/>
+          <t>Net income</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -30066,10 +30068,10 @@
         </is>
       </c>
       <c r="O287" s="5" t="n">
-        <v>-9.152642</v>
+        <v>0.467582</v>
       </c>
       <c r="P287" s="5" t="n">
-        <v>-10.163628</v>
+        <v>9.348188</v>
       </c>
       <c r="Q287" t="inlineStr">
         <is>
@@ -30090,7 +30092,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Net comprehensive loss $</t>
+          <t>Exchange differences on translation of subsidiaries</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -30145,10 +30147,10 @@
         </is>
       </c>
       <c r="O288" s="5" t="n">
-        <v>-8.68506</v>
+        <v>-9.152642</v>
       </c>
       <c r="P288" s="5" t="n">
-        <v>-0.8154400000000001</v>
+        <v>-10.163628</v>
       </c>
       <c r="Q288" t="inlineStr">
         <is>
@@ -30164,19 +30166,15 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Non-controlling interest 18 $</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Net comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -30228,10 +30226,10 @@
         </is>
       </c>
       <c r="O289" s="5" t="n">
-        <v>-1.576822</v>
+        <v>-8.68506</v>
       </c>
       <c r="P289" s="5" t="n">
-        <v>-2.17865</v>
+        <v>-0.8154400000000001</v>
       </c>
       <c r="Q289" t="inlineStr">
         <is>
@@ -30252,10 +30250,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Lithium Chile Inc. shareholders</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr"/>
+          <t>Non-controlling interest 18 $</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -30307,10 +30309,10 @@
         </is>
       </c>
       <c r="O290" s="5" t="n">
-        <v>-1.10924</v>
+        <v>-1.576822</v>
       </c>
       <c r="P290" s="5" t="n">
-        <v>7.169538</v>
+        <v>-2.17865</v>
       </c>
       <c r="Q290" t="inlineStr">
         <is>
@@ -30331,7 +30333,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Net income (loss) attributable to total</t>
+          <t>Lithium Chile Inc. shareholders</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -30386,10 +30388,10 @@
         </is>
       </c>
       <c r="O291" s="5" t="n">
-        <v>0.467582</v>
+        <v>-1.10924</v>
       </c>
       <c r="P291" s="5" t="n">
-        <v>9.348188</v>
+        <v>7.169538</v>
       </c>
       <c r="Q291" t="inlineStr">
         <is>
@@ -30405,19 +30407,15 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Net comprehensive loss attributable to</t>
+          <t>Net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Non-controlling interest 18 $</t>
-        </is>
-      </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>MinorityInterests</t>
-        </is>
-      </c>
+          <t>Net income (loss) attributable to total</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -30469,10 +30467,10 @@
         </is>
       </c>
       <c r="O292" s="5" t="n">
-        <v>-1.576822</v>
+        <v>0.467582</v>
       </c>
       <c r="P292" s="5" t="n">
-        <v>-2.17865</v>
+        <v>9.348188</v>
       </c>
       <c r="Q292" t="inlineStr">
         <is>
@@ -30493,10 +30491,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Lithium Chile Inc. shareholders</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr"/>
+          <t>Non-controlling interest 18 $</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -30548,10 +30550,10 @@
         </is>
       </c>
       <c r="O293" s="5" t="n">
-        <v>-10.261882</v>
+        <v>-1.576822</v>
       </c>
       <c r="P293" s="5" t="n">
-        <v>-2.99409</v>
+        <v>-2.17865</v>
       </c>
       <c r="Q293" t="inlineStr">
         <is>
@@ -30572,7 +30574,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Net comprehensive loss attributable to total</t>
+          <t>Lithium Chile Inc. shareholders</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -30627,10 +30629,10 @@
         </is>
       </c>
       <c r="O294" s="5" t="n">
-        <v>-8.68506</v>
+        <v>-10.261882</v>
       </c>
       <c r="P294" s="5" t="n">
-        <v>-0.8154400000000001</v>
+        <v>-2.99409</v>
       </c>
       <c r="Q294" t="inlineStr">
         <is>
@@ -30646,19 +30648,15 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Net income per share                                      9</t>
+          <t>Net comprehensive loss attributable to</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Basic $</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Net comprehensive loss attributable to total</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -30710,10 +30708,10 @@
         </is>
       </c>
       <c r="O295" s="5" t="n">
-        <v>0</v>
+        <v>-8.68506</v>
       </c>
       <c r="P295" s="5" t="n">
-        <v>5e-08</v>
+        <v>-0.8154400000000001</v>
       </c>
       <c r="Q295" t="inlineStr">
         <is>
@@ -30734,12 +30732,12 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Diluted $</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>DilutedEPS</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -30796,7 +30794,7 @@
         <v>0</v>
       </c>
       <c r="P296" s="5" t="n">
-        <v>4e-08</v>
+        <v>5e-08</v>
       </c>
       <c r="Q296" t="inlineStr">
         <is>
@@ -30812,17 +30810,17 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Net income per share                                      9</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>General and administrative 11 $</t>
+          <t>Diluted $</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -30870,16 +30868,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N297" s="5" t="n">
-        <v>4.637598</v>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O297" s="5" t="n">
-        <v>3.877406</v>
-      </c>
-      <c r="P297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P297" s="5" t="n">
+        <v>4e-08</v>
       </c>
       <c r="Q297" t="inlineStr">
         <is>
@@ -30900,10 +30898,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Accretion of notes receivable 8</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>General and administrative 11 $</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -30950,12 +30952,10 @@
         </is>
       </c>
       <c r="N298" s="5" t="n">
-        <v>-0.199221</v>
-      </c>
-      <c r="O298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.637598</v>
+      </c>
+      <c r="O298" s="5" t="n">
+        <v>3.877406</v>
       </c>
       <c r="P298" t="inlineStr">
         <is>
@@ -30981,14 +30981,10 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Depreciation 9</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Accretion of notes receivable 8</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -31035,10 +31031,12 @@
         </is>
       </c>
       <c r="N299" s="5" t="n">
-        <v>0.009546000000000001</v>
-      </c>
-      <c r="O299" s="5" t="n">
-        <v>0.03557</v>
+        <v>-0.199221</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P299" t="inlineStr">
         <is>
@@ -31064,10 +31062,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Share-based compensation 10(e)</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Depreciation 9</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -31114,10 +31116,10 @@
         </is>
       </c>
       <c r="N300" s="5" t="n">
-        <v>2.371927</v>
+        <v>0.009546000000000001</v>
       </c>
       <c r="O300" s="5" t="n">
-        <v>3.079847</v>
+        <v>0.03557</v>
       </c>
       <c r="P300" t="inlineStr">
         <is>
@@ -31143,7 +31145,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable securities 7</t>
+          <t>Share-based compensation 10(e)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -31193,10 +31195,10 @@
         </is>
       </c>
       <c r="N301" s="5" t="n">
-        <v>0.849405</v>
+        <v>2.371927</v>
       </c>
       <c r="O301" s="5" t="n">
-        <v>0.97717</v>
+        <v>3.079847</v>
       </c>
       <c r="P301" t="inlineStr">
         <is>
@@ -31222,14 +31224,10 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Unrealized loss on marketable securities 7</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -31270,14 +31268,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M302" s="5" t="n">
-        <v>1.361957</v>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N302" s="5" t="n">
-        <v>0.356525</v>
+        <v>0.849405</v>
       </c>
       <c r="O302" s="5" t="n">
-        <v>0.006495</v>
+        <v>0.97717</v>
       </c>
       <c r="P302" t="inlineStr">
         <is>
@@ -31303,10 +31303,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Currency gain 14</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Foreign exchange (gain) loss</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -31347,16 +31351,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M303" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M303" s="5" t="n">
+        <v>1.361957</v>
       </c>
       <c r="N303" s="5" t="n">
-        <v>-4.786223</v>
+        <v>0.356525</v>
       </c>
       <c r="O303" s="5" t="n">
-        <v>-2.996778</v>
+        <v>0.006495</v>
       </c>
       <c r="P303" t="inlineStr">
         <is>
@@ -31382,7 +31384,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Change in net monetary position due to hyperinflation 2(b)</t>
+          <t>Currency gain 14</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -31432,10 +31434,10 @@
         </is>
       </c>
       <c r="N304" s="5" t="n">
-        <v>-0.418924</v>
+        <v>-4.786223</v>
       </c>
       <c r="O304" s="5" t="n">
-        <v>-4.214396</v>
+        <v>-2.996778</v>
       </c>
       <c r="P304" t="inlineStr">
         <is>
@@ -31461,7 +31463,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Loss on disposal of property 9</t>
+          <t>Change in net monetary position due to hyperinflation 2(b)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -31511,12 +31513,10 @@
         </is>
       </c>
       <c r="N305" s="5" t="n">
-        <v>0.453577</v>
-      </c>
-      <c r="O305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.418924</v>
+      </c>
+      <c r="O305" s="5" t="n">
+        <v>-4.214396</v>
       </c>
       <c r="P305" t="inlineStr">
         <is>
@@ -31542,14 +31542,10 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Loss on disposal of property 9</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -31560,32 +31556,48 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G306" s="5" t="n">
-        <v>0.039857</v>
-      </c>
-      <c r="H306" s="5" t="n">
-        <v>0.081159</v>
-      </c>
-      <c r="I306" s="5" t="n">
-        <v>1.031305</v>
-      </c>
-      <c r="J306" s="5" t="n">
-        <v>3.464636</v>
-      </c>
-      <c r="K306" s="5" t="n">
-        <v>2.364892</v>
-      </c>
-      <c r="L306" s="5" t="n">
-        <v>0.550807</v>
-      </c>
-      <c r="M306" s="5" t="n">
-        <v>4.642769</v>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N306" s="5" t="n">
-        <v>3.27421</v>
-      </c>
-      <c r="O306" s="5" t="n">
-        <v>0.765314</v>
+        <v>0.453577</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
@@ -31606,17 +31618,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Interest income 19</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -31629,46 +31641,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G307" s="5" t="n">
+        <v>0.039857</v>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>0.081159</v>
+      </c>
+      <c r="I307" s="5" t="n">
+        <v>1.031305</v>
+      </c>
+      <c r="J307" s="5" t="n">
+        <v>3.464636</v>
+      </c>
+      <c r="K307" s="5" t="n">
+        <v>2.364892</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>0.550807</v>
+      </c>
+      <c r="M307" s="5" t="n">
+        <v>4.642769</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>2.221301</v>
+        <v>3.27421</v>
       </c>
       <c r="O307" s="5" t="n">
-        <v>1.185444</v>
+        <v>0.765314</v>
       </c>
       <c r="P307" t="inlineStr">
         <is>
@@ -31694,10 +31692,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Net Income (loss) before tax</t>
-        </is>
-      </c>
-      <c r="D308" t="inlineStr"/>
+          <t>Interest income 19</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -31744,10 +31746,10 @@
         </is>
       </c>
       <c r="N308" s="5" t="n">
-        <v>-1.052909</v>
+        <v>2.221301</v>
       </c>
       <c r="O308" s="5" t="n">
-        <v>0.42013</v>
+        <v>1.185444</v>
       </c>
       <c r="P308" t="inlineStr">
         <is>
@@ -31773,7 +31775,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Deferred income tax 17</t>
+          <t>Net Income (loss) before tax</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -31822,13 +31824,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N309" s="5" t="n">
+        <v>-1.052909</v>
       </c>
       <c r="O309" s="5" t="n">
-        <v>1.018044</v>
+        <v>0.42013</v>
       </c>
       <c r="P309" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Current income tax (recovery) expense 17</t>
+          <t>Deferred income tax 17</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -31903,11 +31903,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N310" s="5" t="n">
-        <v>1.065496</v>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O310" s="5" t="n">
-        <v>-1.065496</v>
+        <v>1.018044</v>
       </c>
       <c r="P310" t="inlineStr">
         <is>
@@ -31933,10 +31935,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Net income after tax</t>
-        </is>
-      </c>
-      <c r="D311" t="inlineStr"/>
+          <t>Current income tax (recovery) expense 17</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E311" t="inlineStr">
         <is>
           <t>-</t>
@@ -31983,10 +31989,10 @@
         </is>
       </c>
       <c r="N311" s="5" t="n">
-        <v>-2.118405</v>
+        <v>1.065496</v>
       </c>
       <c r="O311" s="5" t="n">
-        <v>0.467582</v>
+        <v>-1.065496</v>
       </c>
       <c r="P311" t="inlineStr">
         <is>
@@ -32007,12 +32013,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment</t>
+          <t>Net income after tax</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -32046,20 +32052,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K312" s="5" t="n">
-        <v>-0.806565</v>
-      </c>
-      <c r="L312" s="5" t="n">
-        <v>-0.099261</v>
-      </c>
-      <c r="M312" s="5" t="n">
-        <v>0.319283</v>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N312" s="5" t="n">
-        <v>-1.571977</v>
+        <v>-2.118405</v>
       </c>
       <c r="O312" s="5" t="n">
-        <v>-9.152642</v>
+        <v>0.467582</v>
       </c>
       <c r="P312" t="inlineStr">
         <is>
@@ -32085,14 +32097,10 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>NET LOSS AND OTHER COMPREHENSIVE LOSS $</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Foreign exchange translation adjustment</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -32123,26 +32131,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K313" s="5" t="n">
+        <v>-0.806565</v>
+      </c>
+      <c r="L313" s="5" t="n">
+        <v>-0.099261</v>
+      </c>
+      <c r="M313" s="5" t="n">
+        <v>0.319283</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>-3.690382</v>
+        <v>-1.571977</v>
       </c>
       <c r="O313" s="5" t="n">
-        <v>-8.68506</v>
+        <v>-9.152642</v>
       </c>
       <c r="P313" t="inlineStr">
         <is>
@@ -32163,17 +32165,17 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Total net income (loss) attributable to</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Non-controlling interest 3(d)</t>
+          <t>NET LOSS AND OTHER COMPREHENSIVE LOSS $</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>MinorityInterests</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -32221,13 +32223,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N314" s="5" t="n">
+        <v>-3.690382</v>
       </c>
       <c r="O314" s="5" t="n">
-        <v>-1.576822</v>
+        <v>-8.68506</v>
       </c>
       <c r="P314" t="inlineStr">
         <is>
@@ -32253,10 +32253,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Shareholders of the Corporation</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr"/>
+          <t>Non-controlling interest 3(d)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>MinorityInterests</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -32302,11 +32306,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N315" s="5" t="n">
-        <v>-2.118405</v>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O315" s="5" t="n">
-        <v>-1.10924</v>
+        <v>-1.576822</v>
       </c>
       <c r="P315" t="inlineStr">
         <is>
@@ -32332,7 +32338,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Total net income (loss) attributable to total</t>
+          <t>Shareholders of the Corporation</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -32385,7 +32391,7 @@
         <v>-2.118405</v>
       </c>
       <c r="O316" s="5" t="n">
-        <v>0.467582</v>
+        <v>-1.10924</v>
       </c>
       <c r="P316" t="inlineStr">
         <is>
@@ -32406,12 +32412,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Non-controlling interest                                                   3(d)              1,576,822                         --</t>
+          <t>Total net income (loss) attributable to</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Shareholders of the Corporation</t>
+          <t>Total net income (loss) attributable to total</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -32461,10 +32467,10 @@
         </is>
       </c>
       <c r="N317" s="5" t="n">
-        <v>-3.690382</v>
+        <v>-2.118405</v>
       </c>
       <c r="O317" s="5" t="n">
-        <v>-10.261882</v>
+        <v>0.467582</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
@@ -32490,7 +32496,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Non-controlling interest                                                   3(d)              1,576,822                         -- total</t>
+          <t>Shareholders of the Corporation</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -32543,7 +32549,7 @@
         <v>-3.690382</v>
       </c>
       <c r="O318" s="5" t="n">
-        <v>-8.68506</v>
+        <v>-10.261882</v>
       </c>
       <c r="P318" t="inlineStr">
         <is>
@@ -32569,7 +32575,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted 10(d)</t>
+          <t>Non-controlling interest                                                   3(d)              1,576,822                         -- total</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -32619,10 +32625,10 @@
         </is>
       </c>
       <c r="N319" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-3.690382</v>
       </c>
       <c r="O319" s="5" t="n">
-        <v>-4e-08</v>
+        <v>-8.68506</v>
       </c>
       <c r="P319" t="inlineStr">
         <is>
@@ -32648,14 +32654,10 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 10(d)</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Net loss per share - basic and diluted 10(d)</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -32702,10 +32704,10 @@
         </is>
       </c>
       <c r="N320" s="5" t="n">
-        <v>182.697415</v>
+        <v>-2e-08</v>
       </c>
       <c r="O320" s="5" t="n">
-        <v>204.959776</v>
+        <v>-4e-08</v>
       </c>
       <c r="P320" t="inlineStr">
         <is>
@@ -32726,17 +32728,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>Non-controlling interest                                                   3(d)              1,576,822                         --</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Interest and other income 6 $</t>
+          <t>Weighted average number of shares outstanding 10(d)</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -32779,16 +32781,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M321" s="5" t="n">
-        <v>0.141009</v>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N321" s="5" t="n">
-        <v>2.221301</v>
-      </c>
-      <c r="O321" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>182.697415</v>
+      </c>
+      <c r="O321" s="5" t="n">
+        <v>204.959776</v>
       </c>
       <c r="P321" t="inlineStr">
         <is>
@@ -32814,12 +32816,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>REVENUE total</t>
+          <t>Interest and other income 6 $</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -32847,14 +32849,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J322" s="5" t="n">
-        <v>0.09838</v>
-      </c>
-      <c r="K322" s="5" t="n">
-        <v>0.090506</v>
-      </c>
-      <c r="L322" s="5" t="n">
-        <v>0.00182</v>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M322" s="5" t="n">
         <v>0.141009</v>
@@ -32886,17 +32894,17 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>General and administrative 8</t>
+          <t>REVENUE total</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -32919,23 +32927,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I323" s="5" t="n">
-        <v>0.553861</v>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J323" s="5" t="n">
-        <v>2.866461</v>
+        <v>0.09838</v>
       </c>
       <c r="K323" s="5" t="n">
-        <v>1.082089</v>
+        <v>0.090506</v>
       </c>
       <c r="L323" s="5" t="n">
-        <v>0.550807</v>
+        <v>0.00182</v>
       </c>
       <c r="M323" s="5" t="n">
-        <v>2.146623</v>
+        <v>0.141009</v>
       </c>
       <c r="N323" s="5" t="n">
-        <v>4.637598</v>
+        <v>2.221301</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
@@ -32966,10 +32976,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Accretion of notes receivable 5</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr"/>
+          <t>General and administrative 8</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -32990,27 +33004,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I324" s="5" t="n">
+        <v>0.553861</v>
       </c>
       <c r="J324" s="5" t="n">
-        <v>-0.313434</v>
+        <v>2.866461</v>
       </c>
       <c r="K324" s="5" t="n">
-        <v>-0.558178</v>
-      </c>
-      <c r="L324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.082089</v>
+      </c>
+      <c r="L324" s="5" t="n">
+        <v>0.550807</v>
       </c>
       <c r="M324" s="5" t="n">
-        <v>-0.10975</v>
+        <v>2.146623</v>
       </c>
       <c r="N324" s="5" t="n">
-        <v>-0.199221</v>
+        <v>4.637598</v>
       </c>
       <c r="O324" t="inlineStr">
         <is>
@@ -33041,14 +33051,10 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Depreciation 6</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Accretion of notes receivable 5</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
@@ -33074,28 +33080,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J325" s="5" t="n">
+        <v>-0.313434</v>
+      </c>
+      <c r="K325" s="5" t="n">
+        <v>-0.558178</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M325" s="5" t="n">
+        <v>-0.10975</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>0.009546000000000001</v>
+        <v>-0.199221</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -33126,10 +33126,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Share-based compensation 7(e)</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr"/>
+          <t>Depreciation 6</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E326" t="inlineStr">
         <is>
           <t>-</t>
@@ -33150,25 +33154,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I326" s="5" t="n">
-        <v>0.465149</v>
-      </c>
-      <c r="J326" s="5" t="n">
-        <v>0.696801</v>
-      </c>
-      <c r="K326" s="5" t="n">
-        <v>0.386527</v>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M326" s="5" t="n">
-        <v>0.982468</v>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N326" s="5" t="n">
-        <v>2.371927</v>
+        <v>0.009546000000000001</v>
       </c>
       <c r="O326" t="inlineStr">
         <is>
@@ -33199,7 +33211,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Fair value adjustment on note receivable 5</t>
+          <t>Share-based compensation 7(e)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -33223,18 +33235,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I327" s="5" t="n">
+        <v>0.465149</v>
       </c>
       <c r="J327" s="5" t="n">
-        <v>0.441048</v>
-      </c>
-      <c r="K327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.696801</v>
+      </c>
+      <c r="K327" s="5" t="n">
+        <v>0.386527</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -33242,12 +33250,10 @@
         </is>
       </c>
       <c r="M327" s="5" t="n">
-        <v>0.236471</v>
-      </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.982468</v>
+      </c>
+      <c r="N327" s="5" t="n">
+        <v>2.371927</v>
       </c>
       <c r="O327" t="inlineStr">
         <is>
@@ -33278,7 +33284,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Unrealized loss on marketable security 4</t>
+          <t>Fair value adjustment on note receivable 5</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -33307,10 +33313,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J328" s="5" t="n">
+        <v>0.441048</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -33323,10 +33327,12 @@
         </is>
       </c>
       <c r="M328" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="N328" s="5" t="n">
-        <v>0.849405</v>
+        <v>0.236471</v>
+      </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
@@ -33357,7 +33363,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Currency gain 11</t>
+          <t>Unrealized loss on marketable security 4</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -33401,13 +33407,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M329" s="5" t="n">
+        <v>0.025</v>
       </c>
       <c r="N329" s="5" t="n">
-        <v>-4.786223</v>
+        <v>0.849405</v>
       </c>
       <c r="O329" t="inlineStr">
         <is>
@@ -33438,7 +33442,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Loss on disposal of property 6</t>
+          <t>Currency gain 11</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -33488,7 +33492,7 @@
         </is>
       </c>
       <c r="N330" s="5" t="n">
-        <v>0.453577</v>
+        <v>-4.786223</v>
       </c>
       <c r="O330" t="inlineStr">
         <is>
@@ -33519,7 +33523,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Net loss before tax</t>
+          <t>Loss on disposal of property 6</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -33563,11 +33567,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M331" s="5" t="n">
-        <v>-4.50176</v>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N331" s="5" t="n">
-        <v>-1.052908</v>
+        <v>0.453577</v>
       </c>
       <c r="O331" t="inlineStr">
         <is>
@@ -33598,14 +33604,10 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Current income tax expense 14</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Net loss before tax</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -33646,13 +33648,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M332" s="5" t="n">
+        <v>-4.50176</v>
       </c>
       <c r="N332" s="5" t="n">
-        <v>1.065496</v>
+        <v>-1.052908</v>
       </c>
       <c r="O332" t="inlineStr">
         <is>
@@ -33683,10 +33683,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Net loss after tax</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr"/>
+          <t>Current income tax expense 14</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -33727,11 +33731,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M333" s="5" t="n">
-        <v>-4.50176</v>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N333" s="5" t="n">
-        <v>-2.118404</v>
+        <v>1.065496</v>
       </c>
       <c r="O333" t="inlineStr">
         <is>
@@ -33757,19 +33763,15 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net loss after tax</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr"/>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>
@@ -33811,10 +33813,10 @@
         </is>
       </c>
       <c r="M334" s="5" t="n">
-        <v>-4.182477</v>
+        <v>-4.50176</v>
       </c>
       <c r="N334" s="5" t="n">
-        <v>-3.690381</v>
+        <v>-2.118404</v>
       </c>
       <c r="O334" t="inlineStr">
         <is>
@@ -33845,10 +33847,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted 7(d)</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr"/>
+          <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -33874,20 +33880,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J335" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="K335" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L335" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M335" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-4.182477</v>
       </c>
       <c r="N335" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-3.690381</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
@@ -33918,14 +33930,10 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 7(d)</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Net loss per share - basic and diluted 7(d)</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -33952,19 +33960,19 @@
         </is>
       </c>
       <c r="J336" s="5" t="n">
-        <v>100.623905</v>
+        <v>-3e-08</v>
       </c>
       <c r="K336" s="5" t="n">
-        <v>101.932337</v>
+        <v>-3e-08</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>110.506892</v>
+        <v>-1e-08</v>
       </c>
       <c r="M336" s="5" t="n">
-        <v>138.107886</v>
+        <v>-3e-08</v>
       </c>
       <c r="N336" s="5" t="n">
-        <v>182.697415</v>
+        <v>-2e-08</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
@@ -33990,15 +33998,19 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Interest and other $</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding 7(d)</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E337" t="inlineStr">
         <is>
           <t>-</t>
@@ -34024,26 +34036,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J337" s="5" t="n">
+        <v>100.623905</v>
+      </c>
+      <c r="K337" s="5" t="n">
+        <v>101.932337</v>
       </c>
       <c r="L337" s="5" t="n">
-        <v>0.00182</v>
+        <v>110.506892</v>
       </c>
       <c r="M337" s="5" t="n">
-        <v>0.141009</v>
-      </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>138.107886</v>
+      </c>
+      <c r="N337" s="5" t="n">
+        <v>182.697415</v>
       </c>
       <c r="O337" t="inlineStr">
         <is>
@@ -34069,19 +34075,15 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Foreign exchange loss 6</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Interest and other $</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -34117,13 +34119,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L338" s="5" t="n">
+        <v>0.00182</v>
       </c>
       <c r="M338" s="5" t="n">
-        <v>1.361957</v>
+        <v>0.141009</v>
       </c>
       <c r="N338" t="inlineStr">
         <is>
@@ -34159,10 +34159,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Accretion of notes receivable 4</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr"/>
+          <t>Foreign exchange loss 6</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -34193,8 +34197,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K339" s="5" t="n">
-        <v>-0.558178</v>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -34202,7 +34208,7 @@
         </is>
       </c>
       <c r="M339" s="5" t="n">
-        <v>-0.10975</v>
+        <v>1.361957</v>
       </c>
       <c r="N339" t="inlineStr">
         <is>
@@ -34238,7 +34244,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Fair value adjustment on note receivable 4</t>
+          <t>Accretion of notes receivable 4</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -34272,10 +34278,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K340" s="5" t="n">
+        <v>-0.558178</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -34283,7 +34287,7 @@
         </is>
       </c>
       <c r="M340" s="5" t="n">
-        <v>0.236471</v>
+        <v>-0.10975</v>
       </c>
       <c r="N340" t="inlineStr">
         <is>
@@ -34319,14 +34323,10 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Fair value adjustment on note receivable 4</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr"/>
       <c r="E341" t="inlineStr">
         <is>
           <t>-</t>
@@ -34337,28 +34337,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G341" s="5" t="n">
-        <v>-0.039857</v>
-      </c>
-      <c r="H341" s="5" t="n">
-        <v>-0.081159</v>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J341" s="5" t="n">
-        <v>-3.366255</v>
-      </c>
-      <c r="K341" s="5" t="n">
-        <v>-2.274387</v>
-      </c>
-      <c r="L341" s="5" t="n">
-        <v>-0.548987</v>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M341" s="5" t="n">
-        <v>-4.50176</v>
+        <v>0.236471</v>
       </c>
       <c r="N341" t="inlineStr">
         <is>
@@ -34389,12 +34399,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>NET AND COMPREHENSIVE LOSS $</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -34412,15 +34422,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G342" s="5" t="n">
+        <v>-0.039857</v>
+      </c>
+      <c r="H342" s="5" t="n">
+        <v>-0.081159</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -34431,13 +34437,13 @@
         <v>-3.366255</v>
       </c>
       <c r="K342" s="5" t="n">
-        <v>-3.080952</v>
+        <v>-2.274387</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>-0.648248</v>
+        <v>-0.548987</v>
       </c>
       <c r="M342" s="5" t="n">
-        <v>-4.182477</v>
+        <v>-4.50176</v>
       </c>
       <c r="N342" t="inlineStr">
         <is>
@@ -34468,15 +34474,19 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Interest $</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>NET AND COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -34497,22 +34507,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I343" s="5" t="n">
-        <v>0.007643</v>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J343" s="5" t="n">
-        <v>0.09838</v>
+        <v>-3.366255</v>
       </c>
       <c r="K343" s="5" t="n">
-        <v>0.090506</v>
+        <v>-3.080952</v>
       </c>
       <c r="L343" s="5" t="n">
-        <v>0.00182</v>
-      </c>
-      <c r="M343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.648248</v>
+      </c>
+      <c r="M343" s="5" t="n">
+        <v>-4.182477</v>
       </c>
       <c r="N343" t="inlineStr">
         <is>
@@ -34543,19 +34553,15 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>General and administrative 7</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Interest $</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -34576,21 +34582,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I344" s="5" t="n">
+        <v>0.007643</v>
+      </c>
+      <c r="J344" s="5" t="n">
+        <v>0.09838</v>
       </c>
       <c r="K344" s="5" t="n">
-        <v>1.082089</v>
+        <v>0.090506</v>
       </c>
       <c r="L344" s="5" t="n">
-        <v>0.550807</v>
+        <v>0.00182</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
@@ -34631,12 +34633,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>General and administrative 7</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -34664,16 +34666,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J345" s="5" t="n">
-        <v>-0.226241</v>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K345" s="5" t="n">
-        <v>-0.06197</v>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.082089</v>
+      </c>
+      <c r="L345" s="5" t="n">
+        <v>0.550807</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
@@ -34714,10 +34716,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Impairment of notes receivable 4</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -34743,13 +34749,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J346" s="5" t="n">
+        <v>-0.226241</v>
       </c>
       <c r="K346" s="5" t="n">
-        <v>1.516424</v>
+        <v>-0.06197</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -34795,7 +34799,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Share-based compensation 6(e)</t>
+          <t>Impairment of notes receivable 4</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -34830,7 +34834,7 @@
         </is>
       </c>
       <c r="K347" s="5" t="n">
-        <v>0.386527</v>
+        <v>1.516424</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -34871,12 +34875,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Net loss per share - basic and diluted 6(d)</t>
+          <t>Share-based compensation 6(e)</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
@@ -34911,10 +34915,12 @@
         </is>
       </c>
       <c r="K348" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L348" s="5" t="n">
-        <v>0</v>
+        <v>0.386527</v>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
@@ -34955,14 +34961,10 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 6(d)</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Net loss per share - basic and diluted 6(d)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -34994,10 +34996,10 @@
         </is>
       </c>
       <c r="K349" s="5" t="n">
-        <v>101.932337</v>
+        <v>-3e-08</v>
       </c>
       <c r="L349" s="5" t="n">
-        <v>110.506892</v>
+        <v>0</v>
       </c>
       <c r="M349" t="inlineStr">
         <is>
@@ -35033,15 +35035,19 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Fair value adjustment of note receivable</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding 6(d)</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -35067,18 +35073,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J350" s="5" t="n">
-        <v>0.441048</v>
-      </c>
-      <c r="K350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" s="5" t="n">
+        <v>101.932337</v>
+      </c>
+      <c r="L350" s="5" t="n">
+        <v>110.506892</v>
       </c>
       <c r="M350" t="inlineStr">
         <is>
@@ -35119,7 +35123,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Impairment of notes receivable 5</t>
+          <t>Fair value adjustment of note receivable</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -35148,13 +35152,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K351" s="5" t="n">
-        <v>1.516424</v>
+      <c r="J351" s="5" t="n">
+        <v>0.441048</v>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -35200,7 +35204,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Impairment of notes receivable 5</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -35224,18 +35228,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I352" s="5" t="n">
-        <v>0.012295</v>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K352" s="5" t="n">
+        <v>1.516424</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -35281,7 +35285,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Accretion of note receivable 5</t>
+          <t>Interest</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -35305,13 +35309,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J353" s="5" t="n">
-        <v>-0.313434</v>
+      <c r="I353" s="5" t="n">
+        <v>0.012295</v>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K353" t="inlineStr">
         <is>
@@ -35362,14 +35366,10 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Accretion of note receivable 5</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -35390,11 +35390,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I354" s="5" t="n">
-        <v>-1.023662</v>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J354" s="5" t="n">
-        <v>-3.366255</v>
+        <v>-0.313434</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
@@ -35445,10 +35447,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Comprehensive loss per share - Basic and diluted 7(d) $</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr"/>
+          <t>Net and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -35470,10 +35476,10 @@
         </is>
       </c>
       <c r="I355" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-1.023662</v>
       </c>
       <c r="J355" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-3.366255</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
@@ -35524,14 +35530,10 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 7(d)</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Comprehensive loss per share - Basic and diluted 7(d) $</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -35553,10 +35555,10 @@
         </is>
       </c>
       <c r="I356" s="5" t="n">
-        <v>80.439848</v>
+        <v>-1e-08</v>
       </c>
       <c r="J356" s="5" t="n">
-        <v>100.623905</v>
+        <v>-3e-08</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
@@ -35602,15 +35604,19 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Interest $ 7,643 $ - $</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding 7(d)</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -35632,12 +35638,10 @@
         </is>
       </c>
       <c r="I357" s="5" t="n">
-        <v>0.007643</v>
-      </c>
-      <c r="J357" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>80.439848</v>
+      </c>
+      <c r="J357" s="5" t="n">
+        <v>100.623905</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -35683,19 +35687,15 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>General and administrative 398,083 8,126</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Interest $ 7,643 $ - $</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -35711,11 +35711,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H358" s="5" t="n">
-        <v>0.07664799999999999</v>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I358" s="5" t="n">
-        <v>0.553861</v>
+        <v>0.007643</v>
       </c>
       <c r="J358" t="inlineStr">
         <is>
@@ -35771,10 +35773,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Interest - 1,238</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
+          <t>General and administrative 398,083 8,126</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -35791,10 +35797,10 @@
         </is>
       </c>
       <c r="H359" s="5" t="n">
-        <v>0.004511</v>
+        <v>0.07664799999999999</v>
       </c>
       <c r="I359" s="5" t="n">
-        <v>0.012295</v>
+        <v>0.553861</v>
       </c>
       <c r="J359" t="inlineStr">
         <is>
@@ -35850,7 +35856,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Share-based compensation (120,146) - 7(e)</t>
+          <t>Interest - 1,238</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -35869,13 +35875,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H360" s="5" t="n">
+        <v>0.004511</v>
       </c>
       <c r="I360" s="5" t="n">
-        <v>0.465149</v>
+        <v>0.012295</v>
       </c>
       <c r="J360" t="inlineStr">
         <is>
@@ -35931,14 +35935,10 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Total expenses 277,937 $ 9,364</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (120,146) - 7(e)</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr"/>
       <c r="E361" t="inlineStr">
         <is>
           <t>-</t>
@@ -35954,11 +35954,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H361" s="5" t="n">
-        <v>0.081159</v>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I361" s="5" t="n">
-        <v>1.031305</v>
+        <v>0.465149</v>
       </c>
       <c r="J361" t="inlineStr">
         <is>
@@ -36014,10 +36016,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Net loss (270,294) (9,364)</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
+          <t>Total expenses 277,937 $ 9,364</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -36034,10 +36040,10 @@
         </is>
       </c>
       <c r="H362" s="5" t="n">
-        <v>-0.081159</v>
+        <v>0.081159</v>
       </c>
       <c r="I362" s="5" t="n">
-        <v>-1.023662</v>
+        <v>1.031305</v>
       </c>
       <c r="J362" t="inlineStr">
         <is>
@@ -36088,12 +36094,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment (7,562) -</t>
+          <t>Net loss (270,294) (9,364)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -36113,12 +36119,10 @@
         </is>
       </c>
       <c r="H363" s="5" t="n">
-        <v>-0.000485</v>
-      </c>
-      <c r="I363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.081159</v>
+      </c>
+      <c r="I363" s="5" t="n">
+        <v>-1.023662</v>
       </c>
       <c r="J363" t="inlineStr">
         <is>
@@ -36174,7 +36178,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $ (277,856) $ (9,364) $</t>
+          <t>Foreign exchange translation adjustment (7,562) -</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -36194,10 +36198,12 @@
         </is>
       </c>
       <c r="H364" s="5" t="n">
-        <v>-0.08164399999999999</v>
-      </c>
-      <c r="I364" s="5" t="n">
-        <v>-1.023662</v>
+        <v>-0.000485</v>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
@@ -36253,7 +36259,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Comprehensive loss per share - Basic and diluted $ (0.003) $ (0.000) 7(d) $</t>
+          <t>Comprehensive loss for the year $ (277,856) $ (9,364) $</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -36273,10 +36279,10 @@
         </is>
       </c>
       <c r="H365" s="5" t="n">
-        <v>-1e-09</v>
+        <v>-0.08164399999999999</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>-1.3e-08</v>
+        <v>-1.023662</v>
       </c>
       <c r="J365" t="inlineStr">
         <is>
@@ -36332,7 +36338,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding 93,007,239 68,750,000 7(d)</t>
+          <t>Comprehensive loss per share - Basic and diluted $ (0.003) $ (0.000) 7(d) $</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -36352,10 +36358,10 @@
         </is>
       </c>
       <c r="H366" s="5" t="n">
-        <v>68.75</v>
+        <v>-1e-09</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>80.439848</v>
+        <v>-1.3e-08</v>
       </c>
       <c r="J366" t="inlineStr">
         <is>
@@ -36406,19 +36412,15 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>General and administrative $ 44,178 $ 14,737 $</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding 93,007,239 68,750,000 7(d)</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr"/>
       <c r="E367" t="inlineStr">
         <is>
           <t>-</t>
@@ -36429,16 +36431,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G367" s="5" t="n">
-        <v>0.031878</v>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H367" s="5" t="n">
-        <v>0.07664799999999999</v>
-      </c>
-      <c r="I367" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>68.75</v>
+      </c>
+      <c r="I367" s="5" t="n">
+        <v>80.439848</v>
       </c>
       <c r="J367" t="inlineStr">
         <is>
@@ -36494,10 +36496,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Interest 2,100 $ -</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr"/>
+          <t>General and administrative $ 44,178 $ 14,737 $</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -36509,10 +36515,10 @@
         </is>
       </c>
       <c r="G368" s="5" t="n">
-        <v>0.007979</v>
+        <v>0.031878</v>
       </c>
       <c r="H368" s="5" t="n">
-        <v>0.004511</v>
+        <v>0.07664799999999999</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -36568,12 +36574,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Other comprehensive (loss) income</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment</t>
+          <t>Interest 2,100 $ -</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -36588,10 +36594,10 @@
         </is>
       </c>
       <c r="G369" s="5" t="n">
-        <v>0.002474</v>
+        <v>0.007979</v>
       </c>
       <c r="H369" s="5" t="n">
-        <v>-0.000485</v>
+        <v>0.004511</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -36652,7 +36658,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year #REF! #REF! $</t>
+          <t>Foreign exchange translation adjustment</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -36667,10 +36673,10 @@
         </is>
       </c>
       <c r="G370" s="5" t="n">
-        <v>-0.037383</v>
+        <v>0.002474</v>
       </c>
       <c r="H370" s="5" t="n">
-        <v>-0.08164399999999999</v>
+        <v>-0.000485</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -36731,7 +36737,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Comprehensive loss per share - Basic and diluted (note 6(c)) #REF! $</t>
+          <t>Comprehensive loss for the year #REF! #REF! $</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -36746,10 +36752,10 @@
         </is>
       </c>
       <c r="G371" s="5" t="n">
-        <v>-1e-09</v>
+        <v>-0.037383</v>
       </c>
       <c r="H371" s="5" t="n">
-        <v>-1e-09</v>
+        <v>-0.08164399999999999</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -36810,14 +36816,10 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (note 6(c)) 68,750,000</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Comprehensive loss per share - Basic and diluted (note 6(c)) #REF! $</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr"/>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -36829,10 +36831,10 @@
         </is>
       </c>
       <c r="G372" s="5" t="n">
-        <v>49.708904</v>
+        <v>-1e-09</v>
       </c>
       <c r="H372" s="5" t="n">
-        <v>68.75</v>
+        <v>-1e-09</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -36888,30 +36890,34 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other comprehensive (loss) income</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>General and administrative $ 14,737 $ 14,081 $</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr"/>
+          <t>Weighted average number of shares outstanding (note 6(c)) 68,750,000</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F373" s="5" t="n">
-        <v>0.052316</v>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G373" s="5" t="n">
-        <v>0.039857</v>
-      </c>
-      <c r="H373" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>49.708904</v>
+      </c>
+      <c r="H373" s="5" t="n">
+        <v>68.75</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -36972,7 +36978,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss for the period $ (14,737) $ (14,081) $</t>
+          <t>General and administrative $ 14,737 $ 14,081 $</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -36982,10 +36988,10 @@
         </is>
       </c>
       <c r="F374" s="5" t="n">
-        <v>-0.052316</v>
+        <v>0.052316</v>
       </c>
       <c r="G374" s="5" t="n">
-        <v>-0.039857</v>
+        <v>0.039857</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
@@ -37051,7 +37057,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Loss per share - Basic and diluted (note 5(c)) $ (0.000) $ (0.001) $</t>
+          <t>Net and comprehensive loss for the period $ (14,737) $ (14,081) $</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -37061,10 +37067,10 @@
         </is>
       </c>
       <c r="F375" s="5" t="n">
-        <v>-3e-09</v>
+        <v>-0.052316</v>
       </c>
       <c r="G375" s="5" t="n">
-        <v>-1e-09</v>
+        <v>-0.039857</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -37130,7 +37136,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (note 5(c)) 50,341,530 15,618,132</t>
+          <t>Loss per share - Basic and diluted (note 5(c)) $ (0.000) $ (0.001) $</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -37140,10 +37146,10 @@
         </is>
       </c>
       <c r="F376" s="5" t="n">
-        <v>16.181507</v>
+        <v>-3e-09</v>
       </c>
       <c r="G376" s="5" t="n">
-        <v>49.708904</v>
+        <v>-1e-09</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
@@ -37209,22 +37215,20 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Pre-exploration costs $ 353,441 $</t>
+          <t>Weighted average number of shares outstanding (note 5(c)) 50,341,530 15,618,132</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
-      <c r="E377" s="5" t="n">
-        <v>0.353441</v>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F377" s="5" t="n">
+        <v>16.181507</v>
+      </c>
+      <c r="G377" s="5" t="n">
+        <v>49.708904</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
@@ -37290,15 +37294,17 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>General and administrative (note 7) (13,080) $ 6,637</t>
+          <t>Pre-exploration costs $ 353,441 $</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
       <c r="E378" s="5" t="n">
-        <v>0.08999</v>
-      </c>
-      <c r="F378" s="5" t="n">
-        <v>0.052316</v>
+        <v>0.353441</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
@@ -37369,17 +37375,15 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 5(d)) - $ 17,500</t>
+          <t>General and administrative (note 7) (13,080) $ 6,637</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
       <c r="E379" s="5" t="n">
-        <v>0.0175</v>
-      </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08999</v>
+      </c>
+      <c r="F379" s="5" t="n">
+        <v>0.052316</v>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -37450,15 +37454,17 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Net comprehensive loss for the period 13,080 (377,578) $</t>
+          <t>Share-based compensation (note 5(d)) - $ 17,500</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
       <c r="E380" s="5" t="n">
-        <v>-0.460931</v>
-      </c>
-      <c r="F380" s="5" t="n">
-        <v>-0.052316</v>
+        <v>0.0175</v>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
@@ -37529,15 +37535,15 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Loss per share - Basic and diluted (note 5(c)) #DIV/0! $ (0.025) $</t>
+          <t>Net comprehensive loss for the period 13,080 (377,578) $</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
       <c r="E381" s="5" t="n">
-        <v>-4.200000000000001e-08</v>
+        <v>-0.460931</v>
       </c>
       <c r="F381" s="5" t="n">
-        <v>-3e-09</v>
+        <v>-0.052316</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -37608,67 +37614,146 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (note 5(c)) 15,000,000</t>
+          <t>Loss per share - Basic and diluted (note 5(c)) #DIV/0! $ (0.025) $</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
       <c r="E382" s="5" t="n">
+        <v>-4.200000000000001e-08</v>
+      </c>
+      <c r="F382" s="5" t="n">
+        <v>-3e-09</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares outstanding (note 5(c)) 15,000,000</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" s="5" t="n">
         <v>11.008753</v>
       </c>
-      <c r="F382" s="5" t="n">
+      <c r="F383" s="5" t="n">
         <v>16.181507</v>
       </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q382" t="inlineStr">
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
         <is>
           <t>-</t>
         </is>
